--- a/research/traditional_assets/database/data/south_africa/south_africa_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_software_system_application.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.141</v>
+        <v>-0.0387</v>
       </c>
       <c r="E2">
-        <v>-0.113</v>
+        <v>-0.0111</v>
       </c>
       <c r="G2">
-        <v>0.2541322314049587</v>
+        <v>0.1651260504201681</v>
       </c>
       <c r="H2">
-        <v>0.2541322314049587</v>
+        <v>0.1651260504201681</v>
       </c>
       <c r="I2">
-        <v>0.2520661157024793</v>
+        <v>0.1838235294117647</v>
       </c>
       <c r="J2">
-        <v>0.1807041545677909</v>
+        <v>0.1528700189753321</v>
       </c>
       <c r="K2">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="L2">
-        <v>0.2190082644628099</v>
+        <v>0.2710084033613446</v>
       </c>
       <c r="M2">
-        <v>0.756</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>0.0663157894736842</v>
+        <v>0.1065420560747664</v>
       </c>
       <c r="O2">
-        <v>0.7132075471698113</v>
+        <v>0.883720930232558</v>
       </c>
       <c r="P2">
-        <v>0.756</v>
+        <v>1.14</v>
       </c>
       <c r="Q2">
-        <v>0.0663157894736842</v>
+        <v>0.1065420560747664</v>
       </c>
       <c r="R2">
-        <v>0.7132075471698113</v>
+        <v>0.883720930232558</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.07</v>
+        <v>1.59</v>
       </c>
       <c r="V2">
-        <v>0.2692982456140351</v>
+        <v>0.1485981308411215</v>
       </c>
       <c r="W2">
-        <v>0.2560386473429952</v>
+        <v>0.2828947368421053</v>
       </c>
       <c r="X2">
-        <v>0.1853530585031831</v>
+        <v>0.1538489760924972</v>
       </c>
       <c r="Y2">
-        <v>0.07068558883981207</v>
+        <v>0.1290457607496081</v>
       </c>
       <c r="Z2">
-        <v>5.438202247191013</v>
+        <v>3.194630872483222</v>
       </c>
       <c r="AA2">
-        <v>0.9827057394473128</v>
+        <v>0.4883632820956917</v>
       </c>
       <c r="AB2">
-        <v>0.1853530585031831</v>
+        <v>0.1538489760924972</v>
       </c>
       <c r="AC2">
-        <v>0.7973526809441296</v>
+        <v>0.3345143060031944</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-3.07</v>
+        <v>-1.59</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.368547418967587</v>
+        <v>-0.1745334796926455</v>
       </c>
       <c r="AK2">
-        <v>-2.060402684563758</v>
+        <v>-1.104166666666667</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.036</v>
+        <v>-0.1</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-2.495934959349593</v>
+        <v>-1.751101321585903</v>
       </c>
       <c r="AQ2">
-        <v>-33.88888888888889</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.141</v>
+        <v>-0.0387</v>
       </c>
       <c r="E3">
-        <v>-0.113</v>
+        <v>-0.0111</v>
       </c>
       <c r="G3">
-        <v>0.2541322314049587</v>
+        <v>0.1651260504201681</v>
       </c>
       <c r="H3">
-        <v>0.2541322314049587</v>
+        <v>0.1651260504201681</v>
       </c>
       <c r="I3">
-        <v>0.2520661157024793</v>
+        <v>0.1838235294117647</v>
       </c>
       <c r="J3">
-        <v>0.1807041545677909</v>
+        <v>0.1528700189753321</v>
       </c>
       <c r="K3">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="L3">
-        <v>0.2190082644628099</v>
+        <v>0.2710084033613446</v>
       </c>
       <c r="M3">
-        <v>0.756</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>0.0663157894736842</v>
+        <v>0.1065420560747664</v>
       </c>
       <c r="O3">
-        <v>0.7132075471698113</v>
+        <v>0.883720930232558</v>
       </c>
       <c r="P3">
-        <v>0.756</v>
+        <v>1.14</v>
       </c>
       <c r="Q3">
-        <v>0.0663157894736842</v>
+        <v>0.1065420560747664</v>
       </c>
       <c r="R3">
-        <v>0.7132075471698113</v>
+        <v>0.883720930232558</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.07</v>
+        <v>1.59</v>
       </c>
       <c r="V3">
-        <v>0.2692982456140351</v>
+        <v>0.1485981308411215</v>
       </c>
       <c r="W3">
-        <v>0.2560386473429952</v>
+        <v>0.2828947368421053</v>
       </c>
       <c r="X3">
-        <v>0.1853530585031831</v>
+        <v>0.1538489760924972</v>
       </c>
       <c r="Y3">
-        <v>0.07068558883981207</v>
+        <v>0.1290457607496081</v>
       </c>
       <c r="Z3">
-        <v>5.438202247191013</v>
+        <v>3.194630872483222</v>
       </c>
       <c r="AA3">
-        <v>0.9827057394473128</v>
+        <v>0.4883632820956917</v>
       </c>
       <c r="AB3">
-        <v>0.1853530585031831</v>
+        <v>0.1538489760924972</v>
       </c>
       <c r="AC3">
-        <v>0.7973526809441296</v>
+        <v>0.3345143060031944</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.07</v>
+        <v>-1.59</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.368547418967587</v>
+        <v>-0.1745334796926455</v>
       </c>
       <c r="AK3">
-        <v>-2.060402684563758</v>
+        <v>-1.104166666666667</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.036</v>
+        <v>-0.1</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.495934959349593</v>
+        <v>-1.751101321585903</v>
       </c>
       <c r="AQ3">
-        <v>-33.88888888888889</v>
+        <v>-8.75</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_africa/south_africa_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_software_system_application.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1525017340920423</v>
+        <v>0.1521228294099938</v>
       </c>
       <c r="C2">
-        <v>15.2</v>
+        <v>15.09657348929651</v>
       </c>
       <c r="D2">
-        <v>13.63</v>
+        <v>13.67857348929651</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="G2">
         <v>1.57</v>
@@ -1451,28 +1451,28 @@
         <v>1.03</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0076456</v>
       </c>
       <c r="N2">
-        <v>1.03</v>
+        <v>1.0223544</v>
       </c>
       <c r="O2">
-        <v>0.2781</v>
+        <v>0.276035688</v>
       </c>
       <c r="P2">
-        <v>0.7519</v>
+        <v>0.746318712</v>
       </c>
       <c r="Q2">
-        <v>0.7819</v>
+        <v>0.776318712</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1525017340920423</v>
+        <v>0.1532885246565594</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.287684828229972</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.7180077430156</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1521228294099938</v>
+        <v>0.1517439247279453</v>
       </c>
       <c r="C3">
-        <v>15.09657348929651</v>
+        <v>14.99349442130982</v>
       </c>
       <c r="D3">
-        <v>13.67857348929651</v>
+        <v>13.72749442130982</v>
       </c>
       <c r="E3">
-        <v>0.152</v>
+        <v>0.304</v>
       </c>
       <c r="F3">
-        <v>0.152</v>
+        <v>0.304</v>
       </c>
       <c r="G3">
         <v>1.57</v>
@@ -1533,28 +1533,28 @@
         <v>1.03</v>
       </c>
       <c r="M3">
-        <v>0.0076456</v>
+        <v>0.0152912</v>
       </c>
       <c r="N3">
-        <v>1.0223544</v>
+        <v>1.0147088</v>
       </c>
       <c r="O3">
-        <v>0.276035688</v>
+        <v>0.273971376</v>
       </c>
       <c r="P3">
-        <v>0.746318712</v>
+        <v>0.740737424</v>
       </c>
       <c r="Q3">
-        <v>0.776318712</v>
+        <v>0.770737424</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1532885246565594</v>
+        <v>0.1540913721713728</v>
       </c>
       <c r="T3">
-        <v>1.287684828229972</v>
+        <v>1.297302734583329</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.7180077430156</v>
+        <v>67.3590038715078</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1517439247279453</v>
+        <v>0.1513650200458968</v>
       </c>
       <c r="C4">
-        <v>14.99349442130982</v>
+        <v>14.8907665372699</v>
       </c>
       <c r="D4">
-        <v>13.72749442130982</v>
+        <v>13.7767665372699</v>
       </c>
       <c r="E4">
-        <v>0.304</v>
+        <v>0.456</v>
       </c>
       <c r="F4">
-        <v>0.304</v>
+        <v>0.456</v>
       </c>
       <c r="G4">
         <v>1.57</v>
@@ -1615,28 +1615,28 @@
         <v>1.03</v>
       </c>
       <c r="M4">
-        <v>0.0152912</v>
+        <v>0.0229368</v>
       </c>
       <c r="N4">
-        <v>1.0147088</v>
+        <v>1.0070632</v>
       </c>
       <c r="O4">
-        <v>0.273971376</v>
+        <v>0.271907064</v>
       </c>
       <c r="P4">
-        <v>0.740737424</v>
+        <v>0.735156136</v>
       </c>
       <c r="Q4">
-        <v>0.770737424</v>
+        <v>0.765156136</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1540913721713728</v>
+        <v>0.1549107732431926</v>
       </c>
       <c r="T4">
-        <v>1.297302734583329</v>
+        <v>1.307118948284177</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.3590038715078</v>
+        <v>44.9060025810052</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1513650200458968</v>
+        <v>0.1509861153638483</v>
       </c>
       <c r="C5">
-        <v>14.8907665372699</v>
+        <v>14.7883936323138</v>
       </c>
       <c r="D5">
-        <v>13.7767665372699</v>
+        <v>13.8263936323138</v>
       </c>
       <c r="E5">
-        <v>0.456</v>
+        <v>0.608</v>
       </c>
       <c r="F5">
-        <v>0.456</v>
+        <v>0.608</v>
       </c>
       <c r="G5">
         <v>1.57</v>
@@ -1697,28 +1697,28 @@
         <v>1.03</v>
       </c>
       <c r="M5">
-        <v>0.0229368</v>
+        <v>0.0305824</v>
       </c>
       <c r="N5">
-        <v>1.0070632</v>
+        <v>0.9994176</v>
       </c>
       <c r="O5">
-        <v>0.271907064</v>
+        <v>0.269842752</v>
       </c>
       <c r="P5">
-        <v>0.735156136</v>
+        <v>0.7295748479999999</v>
       </c>
       <c r="Q5">
-        <v>0.765156136</v>
+        <v>0.759574848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1549107732431926</v>
+        <v>0.1557472451706753</v>
       </c>
       <c r="T5">
-        <v>1.307118948284177</v>
+        <v>1.317139666437127</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.9060025810052</v>
+        <v>33.6795019357539</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1509861153638483</v>
+        <v>0.1506072106817997</v>
       </c>
       <c r="C6">
-        <v>14.7883936323138</v>
+        <v>14.68637955646014</v>
       </c>
       <c r="D6">
-        <v>13.8263936323138</v>
+        <v>13.87637955646014</v>
       </c>
       <c r="E6">
-        <v>0.608</v>
+        <v>0.76</v>
       </c>
       <c r="F6">
-        <v>0.608</v>
+        <v>0.76</v>
       </c>
       <c r="G6">
         <v>1.57</v>
@@ -1779,28 +1779,28 @@
         <v>1.03</v>
       </c>
       <c r="M6">
-        <v>0.0305824</v>
+        <v>0.038228</v>
       </c>
       <c r="N6">
-        <v>0.9994176</v>
+        <v>0.991772</v>
       </c>
       <c r="O6">
-        <v>0.269842752</v>
+        <v>0.26777844</v>
       </c>
       <c r="P6">
-        <v>0.7295748479999999</v>
+        <v>0.72399356</v>
       </c>
       <c r="Q6">
-        <v>0.759574848</v>
+        <v>0.7539935600000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1557472451706753</v>
+        <v>0.1566013270334734</v>
       </c>
       <c r="T6">
-        <v>1.317139666437127</v>
+        <v>1.327371347077507</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.6795019357539</v>
+        <v>26.94360154860312</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1506072106817997</v>
+        <v>0.1502283059997512</v>
       </c>
       <c r="C7">
-        <v>14.68637955646014</v>
+        <v>14.5847282156047</v>
       </c>
       <c r="D7">
-        <v>13.87637955646014</v>
+        <v>13.9267282156047</v>
       </c>
       <c r="E7">
-        <v>0.76</v>
+        <v>0.912</v>
       </c>
       <c r="F7">
-        <v>0.76</v>
+        <v>0.912</v>
       </c>
       <c r="G7">
         <v>1.57</v>
@@ -1861,28 +1861,28 @@
         <v>1.03</v>
       </c>
       <c r="M7">
-        <v>0.038228</v>
+        <v>0.0458736</v>
       </c>
       <c r="N7">
-        <v>0.991772</v>
+        <v>0.9841264000000001</v>
       </c>
       <c r="O7">
-        <v>0.26777844</v>
+        <v>0.265714128</v>
       </c>
       <c r="P7">
-        <v>0.72399356</v>
+        <v>0.718412272</v>
       </c>
       <c r="Q7">
-        <v>0.7539935600000001</v>
+        <v>0.748412272</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1566013270334734</v>
+        <v>0.1574735808507992</v>
       </c>
       <c r="T7">
-        <v>1.327371347077507</v>
+        <v>1.337820723050662</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.94360154860312</v>
+        <v>22.4530012905026</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1502283059997512</v>
+        <v>0.1498494013177027</v>
       </c>
       <c r="C8">
-        <v>14.5847282156047</v>
+        <v>14.48344357253786</v>
       </c>
       <c r="D8">
-        <v>13.9267282156047</v>
+        <v>13.97744357253786</v>
       </c>
       <c r="E8">
-        <v>0.9119999999999999</v>
+        <v>1.064</v>
       </c>
       <c r="F8">
-        <v>0.9119999999999999</v>
+        <v>1.064</v>
       </c>
       <c r="G8">
         <v>1.57</v>
@@ -1943,28 +1943,28 @@
         <v>1.03</v>
       </c>
       <c r="M8">
-        <v>0.04587359999999999</v>
+        <v>0.05351919999999999</v>
       </c>
       <c r="N8">
-        <v>0.9841264000000001</v>
+        <v>0.9764808</v>
       </c>
       <c r="O8">
-        <v>0.265714128</v>
+        <v>0.263649816</v>
       </c>
       <c r="P8">
-        <v>0.718412272</v>
+        <v>0.712830984</v>
       </c>
       <c r="Q8">
-        <v>0.748412272</v>
+        <v>0.742830984</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1574735808507992</v>
+        <v>0.1583645928147341</v>
       </c>
       <c r="T8">
-        <v>1.337820723050662</v>
+        <v>1.34849481678668</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.4530012905026</v>
+        <v>19.24542967757366</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1498494013177027</v>
+        <v>0.1494704966356542</v>
       </c>
       <c r="C9">
-        <v>14.48344357253787</v>
+        <v>14.38252964798435</v>
       </c>
       <c r="D9">
-        <v>13.97744357253787</v>
+        <v>14.02852964798435</v>
       </c>
       <c r="E9">
-        <v>1.064</v>
+        <v>1.216</v>
       </c>
       <c r="F9">
-        <v>1.064</v>
+        <v>1.216</v>
       </c>
       <c r="G9">
         <v>1.57</v>
@@ -2025,28 +2025,28 @@
         <v>1.03</v>
       </c>
       <c r="M9">
-        <v>0.0535192</v>
+        <v>0.0611648</v>
       </c>
       <c r="N9">
-        <v>0.9764808</v>
+        <v>0.9688352</v>
       </c>
       <c r="O9">
-        <v>0.263649816</v>
+        <v>0.261585504</v>
       </c>
       <c r="P9">
-        <v>0.712830984</v>
+        <v>0.707249696</v>
       </c>
       <c r="Q9">
-        <v>0.742830984</v>
+        <v>0.737249696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1583645928147341</v>
+        <v>0.159274974603972</v>
       </c>
       <c r="T9">
-        <v>1.34849481678668</v>
+        <v>1.359400956038698</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.24542967757366</v>
+        <v>16.83975096787695</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1494704966356542</v>
+        <v>0.1490915919536057</v>
       </c>
       <c r="C10">
-        <v>14.38252964798435</v>
+        <v>14.28199052166577</v>
       </c>
       <c r="D10">
-        <v>14.02852964798435</v>
+        <v>14.07999052166577</v>
       </c>
       <c r="E10">
-        <v>1.216</v>
+        <v>1.368</v>
       </c>
       <c r="F10">
-        <v>1.216</v>
+        <v>1.368</v>
       </c>
       <c r="G10">
         <v>1.57</v>
@@ -2107,28 +2107,28 @@
         <v>1.03</v>
       </c>
       <c r="M10">
-        <v>0.0611648</v>
+        <v>0.06881039999999999</v>
       </c>
       <c r="N10">
-        <v>0.9688352</v>
+        <v>0.9611896</v>
       </c>
       <c r="O10">
-        <v>0.261585504</v>
+        <v>0.259521192</v>
       </c>
       <c r="P10">
-        <v>0.707249696</v>
+        <v>0.701668408</v>
       </c>
       <c r="Q10">
-        <v>0.737249696</v>
+        <v>0.731668408</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.159274974603972</v>
+        <v>0.1602053647841821</v>
       </c>
       <c r="T10">
-        <v>1.359400956038698</v>
+        <v>1.370546790658893</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.83975096787695</v>
+        <v>14.96866752700173</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1490915919536057</v>
+        <v>0.1487126872715572</v>
       </c>
       <c r="C11">
-        <v>14.28199052166577</v>
+        <v>14.18183033338676</v>
       </c>
       <c r="D11">
-        <v>14.07999052166577</v>
+        <v>14.13183033338676</v>
       </c>
       <c r="E11">
-        <v>1.368</v>
+        <v>1.52</v>
       </c>
       <c r="F11">
-        <v>1.368</v>
+        <v>1.52</v>
       </c>
       <c r="G11">
         <v>1.57</v>
@@ -2189,28 +2189,28 @@
         <v>1.03</v>
       </c>
       <c r="M11">
-        <v>0.06881039999999999</v>
+        <v>0.07645599999999998</v>
       </c>
       <c r="N11">
-        <v>0.9611896</v>
+        <v>0.9535440000000001</v>
       </c>
       <c r="O11">
-        <v>0.259521192</v>
+        <v>0.2574568800000001</v>
       </c>
       <c r="P11">
-        <v>0.701668408</v>
+        <v>0.6960871200000001</v>
       </c>
       <c r="Q11">
-        <v>0.731668408</v>
+        <v>0.7260871200000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1602053647841821</v>
+        <v>0.1611564303017302</v>
       </c>
       <c r="T11">
-        <v>1.370546790658893</v>
+        <v>1.381940310492869</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.96866752700173</v>
+        <v>13.47180077430156</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1487126872715572</v>
+        <v>0.1484542325895087</v>
       </c>
       <c r="C12">
-        <v>14.18183033338676</v>
+        <v>14.06541033455616</v>
       </c>
       <c r="D12">
-        <v>14.13183033338676</v>
+        <v>14.16741033455616</v>
       </c>
       <c r="E12">
-        <v>1.52</v>
+        <v>1.672</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.672</v>
       </c>
       <c r="G12">
         <v>1.57</v>
@@ -2271,45 +2271,45 @@
         <v>1.03</v>
       </c>
       <c r="M12">
-        <v>0.076456</v>
+        <v>0.08660959999999999</v>
       </c>
       <c r="N12">
-        <v>0.9535440000000001</v>
+        <v>0.9433904000000001</v>
       </c>
       <c r="O12">
-        <v>0.2574568800000001</v>
+        <v>0.254715408</v>
       </c>
       <c r="P12">
-        <v>0.6960871200000001</v>
+        <v>0.688674992</v>
       </c>
       <c r="Q12">
-        <v>0.7260871200000001</v>
+        <v>0.7186749920000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1611564303017302</v>
+        <v>0.1621288680780996</v>
       </c>
       <c r="T12">
-        <v>1.381940310492869</v>
+        <v>1.393589864480419</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.47180077430156</v>
+        <v>11.89244610297242</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1484542325895087</v>
+        <v>0.1480862779074601</v>
       </c>
       <c r="C13">
-        <v>14.06541033455616</v>
+        <v>13.96437479500724</v>
       </c>
       <c r="D13">
-        <v>14.16741033455616</v>
+        <v>14.21837479500724</v>
       </c>
       <c r="E13">
-        <v>1.672</v>
+        <v>1.824</v>
       </c>
       <c r="F13">
-        <v>1.672</v>
+        <v>1.824</v>
       </c>
       <c r="G13">
         <v>1.57</v>
@@ -2353,28 +2353,28 @@
         <v>1.03</v>
       </c>
       <c r="M13">
-        <v>0.08660959999999999</v>
+        <v>0.09448319999999999</v>
       </c>
       <c r="N13">
-        <v>0.9433904000000001</v>
+        <v>0.9355168</v>
       </c>
       <c r="O13">
-        <v>0.254715408</v>
+        <v>0.252589536</v>
       </c>
       <c r="P13">
-        <v>0.688674992</v>
+        <v>0.682927264</v>
       </c>
       <c r="Q13">
-        <v>0.7186749920000001</v>
+        <v>0.7129272640000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1621288680780996</v>
+        <v>0.1631234067130229</v>
       </c>
       <c r="T13">
-        <v>1.393589864480419</v>
+        <v>1.405504181058594</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.89244610297242</v>
+        <v>10.90140892772472</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1480862779074601</v>
+        <v>0.1477183232254116</v>
       </c>
       <c r="C14">
-        <v>13.96437479500724</v>
+        <v>13.86370724840105</v>
       </c>
       <c r="D14">
-        <v>14.21837479500724</v>
+        <v>14.26970724840104</v>
       </c>
       <c r="E14">
-        <v>1.824</v>
+        <v>1.976</v>
       </c>
       <c r="F14">
-        <v>1.824</v>
+        <v>1.976</v>
       </c>
       <c r="G14">
         <v>1.57</v>
@@ -2435,28 +2435,28 @@
         <v>1.03</v>
       </c>
       <c r="M14">
-        <v>0.09448319999999999</v>
+        <v>0.1023568</v>
       </c>
       <c r="N14">
-        <v>0.9355168</v>
+        <v>0.9276432</v>
       </c>
       <c r="O14">
-        <v>0.252589536</v>
+        <v>0.250463664</v>
       </c>
       <c r="P14">
-        <v>0.682927264</v>
+        <v>0.6771795359999999</v>
       </c>
       <c r="Q14">
-        <v>0.7129272640000001</v>
+        <v>0.7071795359999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1631234067130229</v>
+        <v>0.1641408083050709</v>
       </c>
       <c r="T14">
-        <v>1.405504181058594</v>
+        <v>1.4176923899719</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.90140892772472</v>
+        <v>10.06283901020743</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1477183232254116</v>
+        <v>0.1475241085433631</v>
       </c>
       <c r="C15">
-        <v>13.86370724840105</v>
+        <v>13.7389513962816</v>
       </c>
       <c r="D15">
-        <v>14.26970724840104</v>
+        <v>14.2969513962816</v>
       </c>
       <c r="E15">
-        <v>1.976</v>
+        <v>2.128</v>
       </c>
       <c r="F15">
-        <v>1.976</v>
+        <v>2.128</v>
       </c>
       <c r="G15">
         <v>1.57</v>
@@ -2517,45 +2517,45 @@
         <v>1.03</v>
       </c>
       <c r="M15">
-        <v>0.1023568</v>
+        <v>0.113848</v>
       </c>
       <c r="N15">
-        <v>0.9276432</v>
+        <v>0.9161520000000001</v>
       </c>
       <c r="O15">
-        <v>0.250463664</v>
+        <v>0.24736104</v>
       </c>
       <c r="P15">
-        <v>0.6771795359999999</v>
+        <v>0.66879096</v>
       </c>
       <c r="Q15">
-        <v>0.7071795359999999</v>
+        <v>0.6987909600000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1641408083050709</v>
+        <v>0.1651818703992594</v>
       </c>
       <c r="T15">
-        <v>1.4176923899719</v>
+        <v>1.430164045604119</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.06283901020743</v>
+        <v>9.047150586747243</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1475241085433631</v>
+        <v>0.1471685638613146</v>
       </c>
       <c r="C16">
-        <v>13.7389513962816</v>
+        <v>13.63709716973272</v>
       </c>
       <c r="D16">
-        <v>14.2969513962816</v>
+        <v>14.34709716973271</v>
       </c>
       <c r="E16">
-        <v>2.128</v>
+        <v>2.28</v>
       </c>
       <c r="F16">
-        <v>2.128</v>
+        <v>2.28</v>
       </c>
       <c r="G16">
         <v>1.57</v>
@@ -2599,28 +2599,28 @@
         <v>1.03</v>
       </c>
       <c r="M16">
-        <v>0.113848</v>
+        <v>0.12198</v>
       </c>
       <c r="N16">
-        <v>0.9161520000000001</v>
+        <v>0.90802</v>
       </c>
       <c r="O16">
-        <v>0.24736104</v>
+        <v>0.2451654</v>
       </c>
       <c r="P16">
-        <v>0.66879096</v>
+        <v>0.6628546</v>
       </c>
       <c r="Q16">
-        <v>0.6987909600000001</v>
+        <v>0.6928546</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1651818703992594</v>
+        <v>0.1662474280721348</v>
       </c>
       <c r="T16">
-        <v>1.430164045604119</v>
+        <v>1.442929151957097</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.047150586747243</v>
+        <v>8.444007214297425</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1471685638613146</v>
+        <v>0.1468130191792661</v>
       </c>
       <c r="C17">
-        <v>13.63709716973272</v>
+        <v>13.53559594843449</v>
       </c>
       <c r="D17">
-        <v>14.34709716973271</v>
+        <v>14.39759594843449</v>
       </c>
       <c r="E17">
-        <v>2.28</v>
+        <v>2.432</v>
       </c>
       <c r="F17">
-        <v>2.28</v>
+        <v>2.432</v>
       </c>
       <c r="G17">
         <v>1.57</v>
@@ -2681,28 +2681,28 @@
         <v>1.03</v>
       </c>
       <c r="M17">
-        <v>0.12198</v>
+        <v>0.130112</v>
       </c>
       <c r="N17">
-        <v>0.90802</v>
+        <v>0.899888</v>
       </c>
       <c r="O17">
-        <v>0.2451654</v>
+        <v>0.24296976</v>
       </c>
       <c r="P17">
-        <v>0.6628546</v>
+        <v>0.65691824</v>
       </c>
       <c r="Q17">
-        <v>0.6928546</v>
+        <v>0.68691824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1662474280721348</v>
+        <v>0.167338356165793</v>
       </c>
       <c r="T17">
-        <v>1.442929151957097</v>
+        <v>1.455998189413718</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.444007214297427</v>
+        <v>7.916256763403837</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1468130191792661</v>
+        <v>0.1465567544972176</v>
       </c>
       <c r="C18">
-        <v>13.53559594843449</v>
+        <v>13.42021478720515</v>
       </c>
       <c r="D18">
-        <v>14.39759594843449</v>
+        <v>14.43421478720515</v>
       </c>
       <c r="E18">
-        <v>2.432</v>
+        <v>2.584</v>
       </c>
       <c r="F18">
-        <v>2.432</v>
+        <v>2.584</v>
       </c>
       <c r="G18">
         <v>1.57</v>
@@ -2763,45 +2763,45 @@
         <v>1.03</v>
       </c>
       <c r="M18">
-        <v>0.130112</v>
+        <v>0.1403112</v>
       </c>
       <c r="N18">
-        <v>0.899888</v>
+        <v>0.8896888000000001</v>
       </c>
       <c r="O18">
-        <v>0.24296976</v>
+        <v>0.240215976</v>
       </c>
       <c r="P18">
-        <v>0.65691824</v>
+        <v>0.6494728240000001</v>
       </c>
       <c r="Q18">
-        <v>0.68691824</v>
+        <v>0.6794728240000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.167338356165793</v>
+        <v>0.1684555716833947</v>
       </c>
       <c r="T18">
-        <v>1.455998189413718</v>
+        <v>1.469382143435558</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.916256763403837</v>
+        <v>7.340825251298543</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1465567544972176</v>
+        <v>0.146207049815169</v>
       </c>
       <c r="C19">
-        <v>13.42021478720515</v>
+        <v>13.31848727805187</v>
       </c>
       <c r="D19">
-        <v>14.43421478720515</v>
+        <v>14.48448727805187</v>
       </c>
       <c r="E19">
-        <v>2.584</v>
+        <v>2.736</v>
       </c>
       <c r="F19">
-        <v>2.584</v>
+        <v>2.736</v>
       </c>
       <c r="G19">
         <v>1.57</v>
@@ -2845,28 +2845,28 @@
         <v>1.03</v>
       </c>
       <c r="M19">
-        <v>0.1403112</v>
+        <v>0.1485648</v>
       </c>
       <c r="N19">
-        <v>0.8896888000000001</v>
+        <v>0.8814352</v>
       </c>
       <c r="O19">
-        <v>0.240215976</v>
+        <v>0.237987504</v>
       </c>
       <c r="P19">
-        <v>0.6494728240000001</v>
+        <v>0.643447696</v>
       </c>
       <c r="Q19">
-        <v>0.6794728240000001</v>
+        <v>0.673447696</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1684555716833947</v>
+        <v>0.1696000363599623</v>
       </c>
       <c r="T19">
-        <v>1.469382143435558</v>
+        <v>1.483092535360369</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.340825251298543</v>
+        <v>6.9330016262264</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.146207049815169</v>
+        <v>0.1458573451331205</v>
       </c>
       <c r="C20">
-        <v>13.31848727805187</v>
+        <v>13.21711117789119</v>
       </c>
       <c r="D20">
-        <v>14.48448727805187</v>
+        <v>14.53511117789119</v>
       </c>
       <c r="E20">
-        <v>2.736</v>
+        <v>2.888</v>
       </c>
       <c r="F20">
-        <v>2.736</v>
+        <v>2.888</v>
       </c>
       <c r="G20">
         <v>1.57</v>
@@ -2927,28 +2927,28 @@
         <v>1.03</v>
       </c>
       <c r="M20">
-        <v>0.1485648</v>
+        <v>0.1568184</v>
       </c>
       <c r="N20">
-        <v>0.8814352000000001</v>
+        <v>0.8731816</v>
       </c>
       <c r="O20">
-        <v>0.237987504</v>
+        <v>0.235759032</v>
       </c>
       <c r="P20">
-        <v>0.6434476960000001</v>
+        <v>0.637422568</v>
       </c>
       <c r="Q20">
-        <v>0.6734476960000001</v>
+        <v>0.667422568</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1696000363599623</v>
+        <v>0.1707727594236056</v>
       </c>
       <c r="T20">
-        <v>1.483092535360369</v>
+        <v>1.497141455480856</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.933001626226401</v>
+        <v>6.568106803793433</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1458573451331205</v>
+        <v>0.1455076404510721</v>
       </c>
       <c r="C21">
-        <v>13.21711117789119</v>
+        <v>13.11609018421416</v>
       </c>
       <c r="D21">
-        <v>14.53511117789119</v>
+        <v>14.58609018421416</v>
       </c>
       <c r="E21">
-        <v>2.888</v>
+        <v>3.04</v>
       </c>
       <c r="F21">
-        <v>2.888</v>
+        <v>3.04</v>
       </c>
       <c r="G21">
         <v>1.57</v>
@@ -3009,28 +3009,28 @@
         <v>1.03</v>
       </c>
       <c r="M21">
-        <v>0.1568184</v>
+        <v>0.165072</v>
       </c>
       <c r="N21">
-        <v>0.8731816</v>
+        <v>0.864928</v>
       </c>
       <c r="O21">
-        <v>0.235759032</v>
+        <v>0.23353056</v>
       </c>
       <c r="P21">
-        <v>0.637422568</v>
+        <v>0.63139744</v>
       </c>
       <c r="Q21">
-        <v>0.667422568</v>
+        <v>0.66139744</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1707727594236056</v>
+        <v>0.1719748005638401</v>
       </c>
       <c r="T21">
-        <v>1.497141455480856</v>
+        <v>1.511541598604354</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.568106803793433</v>
+        <v>6.239701463603761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1455076404510721</v>
+        <v>0.1453112357690235</v>
       </c>
       <c r="C22">
-        <v>13.11609018421416</v>
+        <v>12.99287865601659</v>
       </c>
       <c r="D22">
-        <v>14.58609018421416</v>
+        <v>14.61487865601659</v>
       </c>
       <c r="E22">
-        <v>3.04</v>
+        <v>3.192</v>
       </c>
       <c r="F22">
-        <v>3.04</v>
+        <v>3.192</v>
       </c>
       <c r="G22">
         <v>1.57</v>
@@ -3091,45 +3091,45 @@
         <v>1.03</v>
       </c>
       <c r="M22">
-        <v>0.165072</v>
+        <v>0.1765176</v>
       </c>
       <c r="N22">
-        <v>0.864928</v>
+        <v>0.8534824</v>
       </c>
       <c r="O22">
-        <v>0.23353056</v>
+        <v>0.230440248</v>
       </c>
       <c r="P22">
-        <v>0.63139744</v>
+        <v>0.623042152</v>
       </c>
       <c r="Q22">
-        <v>0.66139744</v>
+        <v>0.653042152</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1719748005638401</v>
+        <v>0.1732072731253462</v>
       </c>
       <c r="T22">
-        <v>1.511541598604354</v>
+        <v>1.526306302313257</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.239701463603761</v>
+        <v>5.835112192778509</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1453112357690235</v>
+        <v>0.144968831086975</v>
       </c>
       <c r="C23">
-        <v>12.99287865601659</v>
+        <v>12.89134010468489</v>
       </c>
       <c r="D23">
-        <v>14.61487865601659</v>
+        <v>14.66534010468489</v>
       </c>
       <c r="E23">
-        <v>3.192</v>
+        <v>3.344</v>
       </c>
       <c r="F23">
-        <v>3.192</v>
+        <v>3.344</v>
       </c>
       <c r="G23">
         <v>1.57</v>
@@ -3173,28 +3173,28 @@
         <v>1.03</v>
       </c>
       <c r="M23">
-        <v>0.1765176</v>
+        <v>0.1849232</v>
       </c>
       <c r="N23">
-        <v>0.8534824000000001</v>
+        <v>0.8450768</v>
       </c>
       <c r="O23">
-        <v>0.230440248</v>
+        <v>0.228170736</v>
       </c>
       <c r="P23">
-        <v>0.623042152</v>
+        <v>0.6169060639999999</v>
       </c>
       <c r="Q23">
-        <v>0.653042152</v>
+        <v>0.6469060639999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1732072731253462</v>
+        <v>0.1744713475474039</v>
       </c>
       <c r="T23">
-        <v>1.526306302313257</v>
+        <v>1.541449588168543</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.835112192778511</v>
+        <v>5.569879820379487</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.144968831086975</v>
+        <v>0.1446264264049265</v>
       </c>
       <c r="C24">
-        <v>12.89134010468489</v>
+        <v>12.79015122169426</v>
       </c>
       <c r="D24">
-        <v>14.66534010468489</v>
+        <v>14.71615122169426</v>
       </c>
       <c r="E24">
-        <v>3.344</v>
+        <v>3.496</v>
       </c>
       <c r="F24">
-        <v>3.344</v>
+        <v>3.496</v>
       </c>
       <c r="G24">
         <v>1.57</v>
@@ -3255,28 +3255,28 @@
         <v>1.03</v>
       </c>
       <c r="M24">
-        <v>0.1849232</v>
+        <v>0.1933288</v>
       </c>
       <c r="N24">
-        <v>0.8450768</v>
+        <v>0.8366712000000001</v>
       </c>
       <c r="O24">
-        <v>0.228170736</v>
+        <v>0.225901224</v>
       </c>
       <c r="P24">
-        <v>0.6169060639999999</v>
+        <v>0.610769976</v>
       </c>
       <c r="Q24">
-        <v>0.6469060639999999</v>
+        <v>0.6407699760000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1744713475474039</v>
+        <v>0.1757682550713331</v>
       </c>
       <c r="T24">
-        <v>1.541449588168543</v>
+        <v>1.556986206123965</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.569879820379487</v>
+        <v>5.327711132536901</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1446264264049265</v>
+        <v>0.144284021722878</v>
       </c>
       <c r="C25">
-        <v>12.79015122169426</v>
+        <v>12.68931565417672</v>
       </c>
       <c r="D25">
-        <v>14.71615122169426</v>
+        <v>14.76731565417672</v>
       </c>
       <c r="E25">
-        <v>3.496</v>
+        <v>3.648</v>
       </c>
       <c r="F25">
-        <v>3.496</v>
+        <v>3.648</v>
       </c>
       <c r="G25">
         <v>1.57</v>
@@ -3337,28 +3337,28 @@
         <v>1.03</v>
       </c>
       <c r="M25">
-        <v>0.1933288</v>
+        <v>0.2017344</v>
       </c>
       <c r="N25">
-        <v>0.8366712000000001</v>
+        <v>0.8282656</v>
       </c>
       <c r="O25">
-        <v>0.225901224</v>
+        <v>0.223631712</v>
       </c>
       <c r="P25">
-        <v>0.610769976</v>
+        <v>0.604633888</v>
       </c>
       <c r="Q25">
-        <v>0.6407699760000001</v>
+        <v>0.634633888</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1757682550713331</v>
+        <v>0.1770992917406289</v>
       </c>
       <c r="T25">
-        <v>1.556986206123965</v>
+        <v>1.572931682446636</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.327711132536901</v>
+        <v>5.105723168681196</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.144284021722878</v>
+        <v>0.1439416170408294</v>
       </c>
       <c r="C26">
-        <v>12.68931565417672</v>
+        <v>12.58883710016202</v>
       </c>
       <c r="D26">
-        <v>14.76731565417672</v>
+        <v>14.81883710016202</v>
       </c>
       <c r="E26">
-        <v>3.648</v>
+        <v>3.8</v>
       </c>
       <c r="F26">
-        <v>3.648</v>
+        <v>3.8</v>
       </c>
       <c r="G26">
         <v>1.57</v>
@@ -3419,28 +3419,28 @@
         <v>1.03</v>
       </c>
       <c r="M26">
-        <v>0.2017344</v>
+        <v>0.21014</v>
       </c>
       <c r="N26">
-        <v>0.8282656</v>
+        <v>0.81986</v>
       </c>
       <c r="O26">
-        <v>0.223631712</v>
+        <v>0.2213622</v>
       </c>
       <c r="P26">
-        <v>0.604633888</v>
+        <v>0.5984978</v>
       </c>
       <c r="Q26">
-        <v>0.634633888</v>
+        <v>0.6284978</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1770992917406289</v>
+        <v>0.1784658227211059</v>
       </c>
       <c r="T26">
-        <v>1.572931682446636</v>
+        <v>1.589302371471244</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.105723168681197</v>
+        <v>4.901494241933949</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1439416170408294</v>
+        <v>0.143599212358781</v>
       </c>
       <c r="C27">
-        <v>12.58883710016202</v>
+        <v>12.48871930946852</v>
       </c>
       <c r="D27">
-        <v>14.81883710016202</v>
+        <v>14.87071930946852</v>
       </c>
       <c r="E27">
-        <v>3.8</v>
+        <v>3.952</v>
       </c>
       <c r="F27">
-        <v>3.8</v>
+        <v>3.952</v>
       </c>
       <c r="G27">
         <v>1.57</v>
@@ -3501,28 +3501,28 @@
         <v>1.03</v>
       </c>
       <c r="M27">
-        <v>0.21014</v>
+        <v>0.2185456</v>
       </c>
       <c r="N27">
-        <v>0.81986</v>
+        <v>0.8114544</v>
       </c>
       <c r="O27">
-        <v>0.2213622</v>
+        <v>0.219092688</v>
       </c>
       <c r="P27">
-        <v>0.5984978</v>
+        <v>0.592361712</v>
       </c>
       <c r="Q27">
-        <v>0.6284978</v>
+        <v>0.622361712</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1784658227211059</v>
+        <v>0.1798692869713256</v>
       </c>
       <c r="T27">
-        <v>1.589302371471244</v>
+        <v>1.606115511550572</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.901494241933949</v>
+        <v>4.712975232628796</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.143599212358781</v>
+        <v>0.1432568076767324</v>
       </c>
       <c r="C28">
-        <v>12.48871930946852</v>
+        <v>12.38896608461307</v>
       </c>
       <c r="D28">
-        <v>14.87071930946852</v>
+        <v>14.92296608461307</v>
       </c>
       <c r="E28">
-        <v>3.952</v>
+        <v>4.104</v>
       </c>
       <c r="F28">
-        <v>3.952</v>
+        <v>4.104</v>
       </c>
       <c r="G28">
         <v>1.57</v>
@@ -3583,28 +3583,28 @@
         <v>1.03</v>
       </c>
       <c r="M28">
-        <v>0.2185456</v>
+        <v>0.2269512</v>
       </c>
       <c r="N28">
-        <v>0.8114544</v>
+        <v>0.8030488</v>
       </c>
       <c r="O28">
-        <v>0.219092688</v>
+        <v>0.216823176</v>
       </c>
       <c r="P28">
-        <v>0.592361712</v>
+        <v>0.586225624</v>
       </c>
       <c r="Q28">
-        <v>0.622361712</v>
+        <v>0.616225624</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1798692869713256</v>
+        <v>0.1813112022968937</v>
       </c>
       <c r="T28">
-        <v>1.606115511550572</v>
+        <v>1.623389285604676</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.712975232628796</v>
+        <v>4.538420594383286</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1432568076767324</v>
+        <v>0.1434254029946839</v>
       </c>
       <c r="C29">
-        <v>12.38896608461307</v>
+        <v>12.21119469586959</v>
       </c>
       <c r="D29">
-        <v>14.92296608461307</v>
+        <v>14.8971946958696</v>
       </c>
       <c r="E29">
-        <v>4.104</v>
+        <v>4.256</v>
       </c>
       <c r="F29">
-        <v>4.104</v>
+        <v>4.256</v>
       </c>
       <c r="G29">
         <v>1.57</v>
@@ -3665,45 +3665,45 @@
         <v>1.03</v>
       </c>
       <c r="M29">
-        <v>0.2269512</v>
+        <v>0.2459968</v>
       </c>
       <c r="N29">
-        <v>0.8030488</v>
+        <v>0.7840032</v>
       </c>
       <c r="O29">
-        <v>0.216823176</v>
+        <v>0.211680864</v>
       </c>
       <c r="P29">
-        <v>0.586225624</v>
+        <v>0.572322336</v>
       </c>
       <c r="Q29">
-        <v>0.616225624</v>
+        <v>0.6023223360000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1813112022968937</v>
+        <v>0.1827931708259499</v>
       </c>
       <c r="T29">
-        <v>1.623389285604676</v>
+        <v>1.641142886715838</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.538420594383286</v>
+        <v>4.187046335562088</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1434254029946839</v>
+        <v>0.1431012483126354</v>
       </c>
       <c r="C30">
-        <v>12.21119469586959</v>
+        <v>12.10882402225334</v>
       </c>
       <c r="D30">
-        <v>14.8971946958696</v>
+        <v>14.94682402225335</v>
       </c>
       <c r="E30">
-        <v>4.256</v>
+        <v>4.408</v>
       </c>
       <c r="F30">
-        <v>4.256</v>
+        <v>4.408</v>
       </c>
       <c r="G30">
         <v>1.57</v>
@@ -3747,28 +3747,28 @@
         <v>1.03</v>
       </c>
       <c r="M30">
-        <v>0.2459968</v>
+        <v>0.2547824</v>
       </c>
       <c r="N30">
-        <v>0.7840032</v>
+        <v>0.7752176</v>
       </c>
       <c r="O30">
-        <v>0.211680864</v>
+        <v>0.209308752</v>
       </c>
       <c r="P30">
-        <v>0.572322336</v>
+        <v>0.565908848</v>
       </c>
       <c r="Q30">
-        <v>0.6023223360000001</v>
+        <v>0.595908848</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1827931708259499</v>
+        <v>0.1843168849473738</v>
       </c>
       <c r="T30">
-        <v>1.641142886715838</v>
+        <v>1.659396589266751</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.187046335562088</v>
+        <v>4.042665427439258</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1431012483126354</v>
+        <v>0.1435435936305869</v>
       </c>
       <c r="C31">
-        <v>12.10882402225335</v>
+        <v>11.88918114788271</v>
       </c>
       <c r="D31">
-        <v>14.94682402225335</v>
+        <v>14.8791811478827</v>
       </c>
       <c r="E31">
-        <v>4.407999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="F31">
-        <v>4.407999999999999</v>
+        <v>4.56</v>
       </c>
       <c r="G31">
         <v>1.57</v>
@@ -3829,45 +3829,45 @@
         <v>1.03</v>
       </c>
       <c r="M31">
-        <v>0.2547824</v>
+        <v>0.279528</v>
       </c>
       <c r="N31">
-        <v>0.7752176000000001</v>
+        <v>0.750472</v>
       </c>
       <c r="O31">
-        <v>0.209308752</v>
+        <v>0.20262744</v>
       </c>
       <c r="P31">
-        <v>0.5659088480000001</v>
+        <v>0.54784456</v>
       </c>
       <c r="Q31">
-        <v>0.5959088480000001</v>
+        <v>0.5778445600000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1843168849473738</v>
+        <v>0.1858841337579813</v>
       </c>
       <c r="T31">
-        <v>1.659396589266751</v>
+        <v>1.678171826176262</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.042665427439259</v>
+        <v>3.684782919779056</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1435435936305869</v>
+        <v>0.1432449889485384</v>
       </c>
       <c r="C32">
-        <v>11.88918114788271</v>
+        <v>11.78277603381524</v>
       </c>
       <c r="D32">
-        <v>14.8791811478827</v>
+        <v>14.92477603381524</v>
       </c>
       <c r="E32">
-        <v>4.56</v>
+        <v>4.712</v>
       </c>
       <c r="F32">
-        <v>4.56</v>
+        <v>4.712</v>
       </c>
       <c r="G32">
         <v>1.57</v>
@@ -3911,28 +3911,28 @@
         <v>1.03</v>
       </c>
       <c r="M32">
-        <v>0.279528</v>
+        <v>0.2888456</v>
       </c>
       <c r="N32">
-        <v>0.750472</v>
+        <v>0.7411544000000001</v>
       </c>
       <c r="O32">
-        <v>0.20262744</v>
+        <v>0.200111688</v>
       </c>
       <c r="P32">
-        <v>0.54784456</v>
+        <v>0.5410427120000001</v>
       </c>
       <c r="Q32">
-        <v>0.5778445600000001</v>
+        <v>0.5710427120000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1858841337579813</v>
+        <v>0.1874968100703455</v>
       </c>
       <c r="T32">
-        <v>1.678171826176262</v>
+        <v>1.697491272851266</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.684782919779056</v>
+        <v>3.565918954624894</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1432449889485384</v>
+        <v>0.1436004642664898</v>
       </c>
       <c r="C33">
-        <v>11.78277603381524</v>
+        <v>11.5765289548697</v>
       </c>
       <c r="D33">
-        <v>14.92477603381524</v>
+        <v>14.8705289548697</v>
       </c>
       <c r="E33">
-        <v>4.712</v>
+        <v>4.864</v>
       </c>
       <c r="F33">
-        <v>4.712</v>
+        <v>4.864</v>
       </c>
       <c r="G33">
         <v>1.57</v>
@@ -3993,45 +3993,45 @@
         <v>1.03</v>
       </c>
       <c r="M33">
-        <v>0.2888456</v>
+        <v>0.3117824</v>
       </c>
       <c r="N33">
-        <v>0.7411544000000001</v>
+        <v>0.7182176</v>
       </c>
       <c r="O33">
-        <v>0.200111688</v>
+        <v>0.193918752</v>
       </c>
       <c r="P33">
-        <v>0.5410427120000001</v>
+        <v>0.5242988479999999</v>
       </c>
       <c r="Q33">
-        <v>0.5710427120000001</v>
+        <v>0.554298848</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1874968100703455</v>
+        <v>0.1891569180389557</v>
       </c>
       <c r="T33">
-        <v>1.697491272851266</v>
+        <v>1.717378938546123</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.565918954624894</v>
+        <v>3.303586090812054</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1436004642664898</v>
+        <v>0.1433222995844413</v>
       </c>
       <c r="C34">
-        <v>11.5765289548697</v>
+        <v>11.46694444318622</v>
       </c>
       <c r="D34">
-        <v>14.8705289548697</v>
+        <v>14.91294444318623</v>
       </c>
       <c r="E34">
-        <v>4.864</v>
+        <v>5.016</v>
       </c>
       <c r="F34">
-        <v>4.864</v>
+        <v>5.016</v>
       </c>
       <c r="G34">
         <v>1.57</v>
@@ -4075,28 +4075,28 @@
         <v>1.03</v>
       </c>
       <c r="M34">
-        <v>0.3117824</v>
+        <v>0.3215256</v>
       </c>
       <c r="N34">
-        <v>0.7182176</v>
+        <v>0.7084744000000001</v>
       </c>
       <c r="O34">
-        <v>0.193918752</v>
+        <v>0.191288088</v>
       </c>
       <c r="P34">
-        <v>0.5242988479999999</v>
+        <v>0.517186312</v>
       </c>
       <c r="Q34">
-        <v>0.554298848</v>
+        <v>0.547186312</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1891569180389557</v>
+        <v>0.1908665814693155</v>
       </c>
       <c r="T34">
-        <v>1.717378938546123</v>
+        <v>1.737860265903513</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.303586090812054</v>
+        <v>3.203477421393507</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1433222995844413</v>
+        <v>0.1430441349023928</v>
       </c>
       <c r="C35">
-        <v>11.46694444318622</v>
+        <v>11.35760258862204</v>
       </c>
       <c r="D35">
-        <v>14.91294444318623</v>
+        <v>14.95560258862204</v>
       </c>
       <c r="E35">
-        <v>5.016</v>
+        <v>5.168</v>
       </c>
       <c r="F35">
-        <v>5.016</v>
+        <v>5.168</v>
       </c>
       <c r="G35">
         <v>1.57</v>
@@ -4157,28 +4157,28 @@
         <v>1.03</v>
       </c>
       <c r="M35">
-        <v>0.3215256</v>
+        <v>0.3312688</v>
       </c>
       <c r="N35">
-        <v>0.7084744000000001</v>
+        <v>0.6987312</v>
       </c>
       <c r="O35">
-        <v>0.191288088</v>
+        <v>0.188657424</v>
       </c>
       <c r="P35">
-        <v>0.517186312</v>
+        <v>0.510073776</v>
       </c>
       <c r="Q35">
-        <v>0.547186312</v>
+        <v>0.5400737760000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1908665814693155</v>
+        <v>0.1926280528824134</v>
       </c>
       <c r="T35">
-        <v>1.737860265903513</v>
+        <v>1.75896223954446</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.203477421393507</v>
+        <v>3.109257497234874</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1430441349023928</v>
+        <v>0.1427659702203443</v>
       </c>
       <c r="C36">
-        <v>11.35760258862204</v>
+        <v>11.24850547949659</v>
       </c>
       <c r="D36">
-        <v>14.95560258862204</v>
+        <v>14.99850547949659</v>
       </c>
       <c r="E36">
-        <v>5.168</v>
+        <v>5.32</v>
       </c>
       <c r="F36">
-        <v>5.168</v>
+        <v>5.32</v>
       </c>
       <c r="G36">
         <v>1.57</v>
@@ -4239,28 +4239,28 @@
         <v>1.03</v>
       </c>
       <c r="M36">
-        <v>0.3312688</v>
+        <v>0.341012</v>
       </c>
       <c r="N36">
-        <v>0.6987312</v>
+        <v>0.6889879999999999</v>
       </c>
       <c r="O36">
-        <v>0.188657424</v>
+        <v>0.18602676</v>
       </c>
       <c r="P36">
-        <v>0.510073776</v>
+        <v>0.50296124</v>
       </c>
       <c r="Q36">
-        <v>0.5400737760000001</v>
+        <v>0.53296124</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1926280528824134</v>
+        <v>0.1944437234159143</v>
       </c>
       <c r="T36">
-        <v>1.75896223954446</v>
+        <v>1.780713504682052</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.109257497234874</v>
+        <v>3.020421568742448</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1427659702203443</v>
+        <v>0.1445376455382958</v>
       </c>
       <c r="C37">
-        <v>11.24850547949659</v>
+        <v>10.82738338508855</v>
       </c>
       <c r="D37">
-        <v>14.99850547949659</v>
+        <v>14.72938338508855</v>
       </c>
       <c r="E37">
-        <v>5.32</v>
+        <v>5.472</v>
       </c>
       <c r="F37">
-        <v>5.32</v>
+        <v>5.472</v>
       </c>
       <c r="G37">
         <v>1.57</v>
@@ -4321,45 +4321,45 @@
         <v>1.03</v>
       </c>
       <c r="M37">
-        <v>0.341012</v>
+        <v>0.3934368000000001</v>
       </c>
       <c r="N37">
-        <v>0.6889879999999999</v>
+        <v>0.6365631999999999</v>
       </c>
       <c r="O37">
-        <v>0.18602676</v>
+        <v>0.171872064</v>
       </c>
       <c r="P37">
-        <v>0.50296124</v>
+        <v>0.4646911359999999</v>
       </c>
       <c r="Q37">
-        <v>0.53296124</v>
+        <v>0.4946911359999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1944437234159143</v>
+        <v>0.1963161336535872</v>
       </c>
       <c r="T37">
-        <v>1.780713504682052</v>
+        <v>1.803144496855194</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.020421568742448</v>
+        <v>2.617955412406769</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1445376455382958</v>
+        <v>0.1443164208562473</v>
       </c>
       <c r="C38">
-        <v>10.82738338508855</v>
+        <v>10.70845912137511</v>
       </c>
       <c r="D38">
-        <v>14.72938338508855</v>
+        <v>14.76245912137511</v>
       </c>
       <c r="E38">
-        <v>5.472</v>
+        <v>5.624</v>
       </c>
       <c r="F38">
-        <v>5.472</v>
+        <v>5.624</v>
       </c>
       <c r="G38">
         <v>1.57</v>
@@ -4403,28 +4403,28 @@
         <v>1.03</v>
       </c>
       <c r="M38">
-        <v>0.3934368</v>
+        <v>0.4043656</v>
       </c>
       <c r="N38">
-        <v>0.6365632000000001</v>
+        <v>0.6256344</v>
       </c>
       <c r="O38">
-        <v>0.171872064</v>
+        <v>0.168921288</v>
       </c>
       <c r="P38">
-        <v>0.4646911360000001</v>
+        <v>0.456713112</v>
       </c>
       <c r="Q38">
-        <v>0.4946911360000001</v>
+        <v>0.486713112</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1963161336535872</v>
+        <v>0.1982479854861068</v>
       </c>
       <c r="T38">
-        <v>1.803144496855194</v>
+        <v>1.826287584017959</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.617955412406771</v>
+        <v>2.547199860720101</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1443164208562473</v>
+        <v>0.1451770561741988</v>
       </c>
       <c r="C39">
-        <v>10.70845912137511</v>
+        <v>10.42861176717899</v>
       </c>
       <c r="D39">
-        <v>14.76245912137511</v>
+        <v>14.63461176717899</v>
       </c>
       <c r="E39">
-        <v>5.624</v>
+        <v>5.776</v>
       </c>
       <c r="F39">
-        <v>5.624</v>
+        <v>5.776</v>
       </c>
       <c r="G39">
         <v>1.57</v>
@@ -4485,45 +4485,45 @@
         <v>1.03</v>
       </c>
       <c r="M39">
-        <v>0.4043656</v>
+        <v>0.4378208</v>
       </c>
       <c r="N39">
-        <v>0.6256344</v>
+        <v>0.5921792</v>
       </c>
       <c r="O39">
-        <v>0.168921288</v>
+        <v>0.159888384</v>
       </c>
       <c r="P39">
-        <v>0.456713112</v>
+        <v>0.432290816</v>
       </c>
       <c r="Q39">
-        <v>0.486713112</v>
+        <v>0.462290816</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1982479854861068</v>
+        <v>0.2002421551196754</v>
       </c>
       <c r="T39">
-        <v>1.826287584017959</v>
+        <v>1.850177222379523</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.547199860720101</v>
+        <v>2.352560682361368</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1451770561741988</v>
+        <v>0.1449843014921503</v>
       </c>
       <c r="C40">
-        <v>10.42861176717899</v>
+        <v>10.30505265848585</v>
       </c>
       <c r="D40">
-        <v>14.63461176717899</v>
+        <v>14.66305265848585</v>
       </c>
       <c r="E40">
-        <v>5.776</v>
+        <v>5.928</v>
       </c>
       <c r="F40">
-        <v>5.776</v>
+        <v>5.928</v>
       </c>
       <c r="G40">
         <v>1.57</v>
@@ -4567,28 +4567,28 @@
         <v>1.03</v>
       </c>
       <c r="M40">
-        <v>0.4378208</v>
+        <v>0.4493424</v>
       </c>
       <c r="N40">
-        <v>0.5921792</v>
+        <v>0.5806576</v>
       </c>
       <c r="O40">
-        <v>0.159888384</v>
+        <v>0.156777552</v>
       </c>
       <c r="P40">
-        <v>0.432290816</v>
+        <v>0.423880048</v>
       </c>
       <c r="Q40">
-        <v>0.462290816</v>
+        <v>0.453880048</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2002421551196754</v>
+        <v>0.2023017073641808</v>
       </c>
       <c r="T40">
-        <v>1.850177222379523</v>
+        <v>1.874850127572613</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.352560682361368</v>
+        <v>2.292238613582871</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1449843014921503</v>
+        <v>0.1447915468101018</v>
       </c>
       <c r="C41">
-        <v>10.30505265848585</v>
+        <v>10.18160430904718</v>
       </c>
       <c r="D41">
-        <v>14.66305265848585</v>
+        <v>14.69160430904718</v>
       </c>
       <c r="E41">
-        <v>5.928</v>
+        <v>6.08</v>
       </c>
       <c r="F41">
-        <v>5.928</v>
+        <v>6.08</v>
       </c>
       <c r="G41">
         <v>1.57</v>
@@ -4649,28 +4649,28 @@
         <v>1.03</v>
       </c>
       <c r="M41">
-        <v>0.4493424</v>
+        <v>0.4608640000000001</v>
       </c>
       <c r="N41">
-        <v>0.5806576</v>
+        <v>0.569136</v>
       </c>
       <c r="O41">
-        <v>0.156777552</v>
+        <v>0.15366672</v>
       </c>
       <c r="P41">
-        <v>0.423880048</v>
+        <v>0.4154692799999999</v>
       </c>
       <c r="Q41">
-        <v>0.453880048</v>
+        <v>0.44546928</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2023017073641808</v>
+        <v>0.2044299113501696</v>
       </c>
       <c r="T41">
-        <v>1.874850127572613</v>
+        <v>1.900345462938807</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.292238613582871</v>
+        <v>2.2349326482433</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1447915468101018</v>
+        <v>0.1445987921280532</v>
       </c>
       <c r="C42">
-        <v>10.18160430904718</v>
+        <v>10.05826736713095</v>
       </c>
       <c r="D42">
-        <v>14.69160430904718</v>
+        <v>14.72026736713095</v>
       </c>
       <c r="E42">
-        <v>6.08</v>
+        <v>6.232</v>
       </c>
       <c r="F42">
-        <v>6.08</v>
+        <v>6.232</v>
       </c>
       <c r="G42">
         <v>1.57</v>
@@ -4731,28 +4731,28 @@
         <v>1.03</v>
       </c>
       <c r="M42">
-        <v>0.4608640000000001</v>
+        <v>0.4723856000000001</v>
       </c>
       <c r="N42">
-        <v>0.569136</v>
+        <v>0.5576144</v>
       </c>
       <c r="O42">
-        <v>0.15366672</v>
+        <v>0.150555888</v>
       </c>
       <c r="P42">
-        <v>0.4154692799999999</v>
+        <v>0.407058512</v>
       </c>
       <c r="Q42">
-        <v>0.44546928</v>
+        <v>0.437058512</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2044299113501696</v>
+        <v>0.206630257844158</v>
       </c>
       <c r="T42">
-        <v>1.900345462938807</v>
+        <v>1.926705046961482</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.2349326482433</v>
+        <v>2.180422095847121</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1445987921280532</v>
+        <v>0.1444060374460047</v>
       </c>
       <c r="C43">
-        <v>10.05826736713095</v>
+        <v>9.935042486074092</v>
       </c>
       <c r="D43">
-        <v>14.72026736713095</v>
+        <v>14.74904248607409</v>
       </c>
       <c r="E43">
-        <v>6.232</v>
+        <v>6.384</v>
       </c>
       <c r="F43">
-        <v>6.232</v>
+        <v>6.384</v>
       </c>
       <c r="G43">
         <v>1.57</v>
@@ -4813,28 +4813,28 @@
         <v>1.03</v>
       </c>
       <c r="M43">
-        <v>0.4723856000000001</v>
+        <v>0.4839072000000001</v>
       </c>
       <c r="N43">
-        <v>0.5576144</v>
+        <v>0.5460927999999999</v>
       </c>
       <c r="O43">
-        <v>0.150555888</v>
+        <v>0.147445056</v>
       </c>
       <c r="P43">
-        <v>0.407058512</v>
+        <v>0.3986477439999999</v>
       </c>
       <c r="Q43">
-        <v>0.437058512</v>
+        <v>0.4286477439999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.206630257844158</v>
+        <v>0.2089064783551806</v>
       </c>
       <c r="T43">
-        <v>1.926705046961482</v>
+        <v>1.953973582157353</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.180422095847121</v>
+        <v>2.128507284041238</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1444060374460047</v>
+        <v>0.1442132827639562</v>
       </c>
       <c r="C44">
-        <v>9.935042486074092</v>
+        <v>9.811930324332083</v>
       </c>
       <c r="D44">
-        <v>14.74904248607409</v>
+        <v>14.77793032433208</v>
       </c>
       <c r="E44">
-        <v>6.383999999999999</v>
+        <v>6.536</v>
       </c>
       <c r="F44">
-        <v>6.383999999999999</v>
+        <v>6.536</v>
       </c>
       <c r="G44">
         <v>1.57</v>
@@ -4895,28 +4895,28 @@
         <v>1.03</v>
       </c>
       <c r="M44">
-        <v>0.4839072</v>
+        <v>0.4954288</v>
       </c>
       <c r="N44">
-        <v>0.5460928</v>
+        <v>0.5345712</v>
       </c>
       <c r="O44">
-        <v>0.147445056</v>
+        <v>0.144334224</v>
       </c>
       <c r="P44">
-        <v>0.398647744</v>
+        <v>0.390236976</v>
       </c>
       <c r="Q44">
-        <v>0.4286477440000001</v>
+        <v>0.420236976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2089064783551805</v>
+        <v>0.2112625662525548</v>
       </c>
       <c r="T44">
-        <v>1.953973582157352</v>
+        <v>1.98219890806185</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.128507284041238</v>
+        <v>2.07900711464493</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1442132827639562</v>
+        <v>0.1440205280819077</v>
       </c>
       <c r="C45">
-        <v>9.811930324332083</v>
+        <v>9.688931545529211</v>
       </c>
       <c r="D45">
-        <v>14.77793032433208</v>
+        <v>14.80693154552921</v>
       </c>
       <c r="E45">
-        <v>6.536</v>
+        <v>6.688</v>
       </c>
       <c r="F45">
-        <v>6.536</v>
+        <v>6.688</v>
       </c>
       <c r="G45">
         <v>1.57</v>
@@ -4977,28 +4977,28 @@
         <v>1.03</v>
       </c>
       <c r="M45">
-        <v>0.4954288</v>
+        <v>0.5069504</v>
       </c>
       <c r="N45">
-        <v>0.5345712</v>
+        <v>0.5230496</v>
       </c>
       <c r="O45">
-        <v>0.144334224</v>
+        <v>0.141223392</v>
       </c>
       <c r="P45">
-        <v>0.390236976</v>
+        <v>0.381826208</v>
       </c>
       <c r="Q45">
-        <v>0.420236976</v>
+        <v>0.411826208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2112625662525548</v>
+        <v>0.2137028001462637</v>
       </c>
       <c r="T45">
-        <v>1.98219890806185</v>
+        <v>2.011432281320079</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.07900711464493</v>
+        <v>2.031756952948454</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1440205280819077</v>
+        <v>0.1484924733998592</v>
       </c>
       <c r="C46">
-        <v>9.688931545529211</v>
+        <v>8.892134648482727</v>
       </c>
       <c r="D46">
-        <v>14.80693154552921</v>
+        <v>14.16213464848273</v>
       </c>
       <c r="E46">
-        <v>6.688</v>
+        <v>6.84</v>
       </c>
       <c r="F46">
-        <v>6.688</v>
+        <v>6.84</v>
       </c>
       <c r="G46">
         <v>1.57</v>
@@ -5059,45 +5059,45 @@
         <v>1.03</v>
       </c>
       <c r="M46">
-        <v>0.5069504</v>
+        <v>0.6155999999999999</v>
       </c>
       <c r="N46">
-        <v>0.5230496</v>
+        <v>0.4144000000000001</v>
       </c>
       <c r="O46">
-        <v>0.141223392</v>
+        <v>0.111888</v>
       </c>
       <c r="P46">
-        <v>0.381826208</v>
+        <v>0.3025120000000001</v>
       </c>
       <c r="Q46">
-        <v>0.411826208</v>
+        <v>0.3325120000000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2137028001462637</v>
+        <v>0.2162317698179258</v>
       </c>
       <c r="T46">
-        <v>2.011432281320079</v>
+        <v>2.041728686333153</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.031756952948454</v>
+        <v>1.673164392462638</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1484924733998592</v>
+        <v>0.1484033787178107</v>
       </c>
       <c r="C47">
-        <v>8.892134648482727</v>
+        <v>8.752432205341016</v>
       </c>
       <c r="D47">
-        <v>14.16213464848273</v>
+        <v>14.17443220534102</v>
       </c>
       <c r="E47">
-        <v>6.84</v>
+        <v>6.992</v>
       </c>
       <c r="F47">
-        <v>6.84</v>
+        <v>6.992</v>
       </c>
       <c r="G47">
         <v>1.57</v>
@@ -5141,28 +5141,28 @@
         <v>1.03</v>
       </c>
       <c r="M47">
-        <v>0.6155999999999999</v>
+        <v>0.62928</v>
       </c>
       <c r="N47">
-        <v>0.4144000000000001</v>
+        <v>0.4007200000000001</v>
       </c>
       <c r="O47">
-        <v>0.111888</v>
+        <v>0.1081944</v>
       </c>
       <c r="P47">
-        <v>0.3025120000000001</v>
+        <v>0.2925256000000001</v>
       </c>
       <c r="Q47">
-        <v>0.3325120000000001</v>
+        <v>0.3225256000000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2162317698179258</v>
+        <v>0.2188544050329827</v>
       </c>
       <c r="T47">
-        <v>2.041728686333153</v>
+        <v>2.073147180420786</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.673164392462638</v>
+        <v>1.636791253496059</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1484033787178107</v>
+        <v>0.1483142840357622</v>
       </c>
       <c r="C48">
-        <v>8.752432205341016</v>
+        <v>8.612751137696947</v>
       </c>
       <c r="D48">
-        <v>14.17443220534102</v>
+        <v>14.18675113769695</v>
       </c>
       <c r="E48">
-        <v>6.992</v>
+        <v>7.144</v>
       </c>
       <c r="F48">
-        <v>6.992</v>
+        <v>7.144</v>
       </c>
       <c r="G48">
         <v>1.57</v>
@@ -5223,28 +5223,28 @@
         <v>1.03</v>
       </c>
       <c r="M48">
-        <v>0.62928</v>
+        <v>0.64296</v>
       </c>
       <c r="N48">
-        <v>0.4007200000000001</v>
+        <v>0.3870400000000001</v>
       </c>
       <c r="O48">
-        <v>0.1081944</v>
+        <v>0.1045008</v>
       </c>
       <c r="P48">
-        <v>0.2925256000000001</v>
+        <v>0.2825392</v>
       </c>
       <c r="Q48">
-        <v>0.3225256000000001</v>
+        <v>0.3125392000000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2188544050329827</v>
+        <v>0.2215760076146456</v>
       </c>
       <c r="T48">
-        <v>2.073147180420786</v>
+        <v>2.105751278058896</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.636791253496059</v>
+        <v>1.601965907676994</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1483142840357622</v>
+        <v>0.1482251893537136</v>
       </c>
       <c r="C49">
-        <v>8.612751137696947</v>
+        <v>8.473091501331027</v>
       </c>
       <c r="D49">
-        <v>14.18675113769695</v>
+        <v>14.19909150133103</v>
       </c>
       <c r="E49">
-        <v>7.144</v>
+        <v>7.296</v>
       </c>
       <c r="F49">
-        <v>7.144</v>
+        <v>7.296</v>
       </c>
       <c r="G49">
         <v>1.57</v>
@@ -5305,28 +5305,28 @@
         <v>1.03</v>
       </c>
       <c r="M49">
-        <v>0.64296</v>
+        <v>0.65664</v>
       </c>
       <c r="N49">
-        <v>0.3870400000000001</v>
+        <v>0.37336</v>
       </c>
       <c r="O49">
-        <v>0.1045008</v>
+        <v>0.1008072</v>
       </c>
       <c r="P49">
-        <v>0.2825392</v>
+        <v>0.2725528</v>
       </c>
       <c r="Q49">
-        <v>0.3125392000000001</v>
+        <v>0.3025528000000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2215760076146456</v>
+        <v>0.2244022872186801</v>
       </c>
       <c r="T49">
-        <v>2.105751278058896</v>
+        <v>2.139609379452317</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.601965907676994</v>
+        <v>1.568591617933723</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1482251893537136</v>
+        <v>0.1481360946716651</v>
       </c>
       <c r="C50">
-        <v>8.473091501331028</v>
+        <v>8.333453352218029</v>
       </c>
       <c r="D50">
-        <v>14.19909150133103</v>
+        <v>14.21145335221803</v>
       </c>
       <c r="E50">
-        <v>7.295999999999999</v>
+        <v>7.448</v>
       </c>
       <c r="F50">
-        <v>7.295999999999999</v>
+        <v>7.448</v>
       </c>
       <c r="G50">
         <v>1.57</v>
@@ -5387,28 +5387,28 @@
         <v>1.03</v>
       </c>
       <c r="M50">
-        <v>0.6566399999999999</v>
+        <v>0.6703199999999999</v>
       </c>
       <c r="N50">
-        <v>0.3733600000000001</v>
+        <v>0.3596800000000001</v>
       </c>
       <c r="O50">
-        <v>0.1008072</v>
+        <v>0.09711360000000004</v>
       </c>
       <c r="P50">
-        <v>0.2725528000000001</v>
+        <v>0.2625664000000001</v>
       </c>
       <c r="Q50">
-        <v>0.3025528000000001</v>
+        <v>0.2925664000000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2244022872186801</v>
+        <v>0.2273394013169904</v>
       </c>
       <c r="T50">
-        <v>2.139609379452317</v>
+        <v>2.174795249527833</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.568591617933723</v>
+        <v>1.536579544098341</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1481360946716651</v>
+        <v>0.1480469999896166</v>
       </c>
       <c r="C51">
-        <v>8.333453352218029</v>
+        <v>8.193836746527806</v>
       </c>
       <c r="D51">
-        <v>14.21145335221803</v>
+        <v>14.22383674652781</v>
       </c>
       <c r="E51">
-        <v>7.448</v>
+        <v>7.6</v>
       </c>
       <c r="F51">
-        <v>7.448</v>
+        <v>7.6</v>
       </c>
       <c r="G51">
         <v>1.57</v>
@@ -5469,28 +5469,28 @@
         <v>1.03</v>
       </c>
       <c r="M51">
-        <v>0.6703199999999999</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="N51">
-        <v>0.3596800000000001</v>
+        <v>0.3460000000000001</v>
       </c>
       <c r="O51">
-        <v>0.09711360000000004</v>
+        <v>0.09342000000000003</v>
       </c>
       <c r="P51">
-        <v>0.2625664000000001</v>
+        <v>0.25258</v>
       </c>
       <c r="Q51">
-        <v>0.2925664000000001</v>
+        <v>0.2825800000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2273394013169904</v>
+        <v>0.2303939999792332</v>
       </c>
       <c r="T51">
-        <v>2.174795249527833</v>
+        <v>2.21138855440637</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.536579544098341</v>
+        <v>1.505847953216374</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1480469999896166</v>
+        <v>0.172417176400322</v>
       </c>
       <c r="C52">
-        <v>8.193836746527806</v>
+        <v>5.304155962571582</v>
       </c>
       <c r="D52">
-        <v>14.22383674652781</v>
+        <v>11.48615596257158</v>
       </c>
       <c r="E52">
-        <v>7.6</v>
+        <v>7.752</v>
       </c>
       <c r="F52">
-        <v>7.6</v>
+        <v>7.752</v>
       </c>
       <c r="G52">
         <v>1.57</v>
@@ -5551,45 +5551,45 @@
         <v>1.03</v>
       </c>
       <c r="M52">
-        <v>0.6839999999999999</v>
+        <v>1.1379936</v>
       </c>
       <c r="N52">
-        <v>0.3460000000000001</v>
+        <v>-0.1079936000000001</v>
       </c>
       <c r="O52">
-        <v>0.09342000000000003</v>
+        <v>-0.02915827200000004</v>
       </c>
       <c r="P52">
-        <v>0.25258</v>
+        <v>-0.07883532800000009</v>
       </c>
       <c r="Q52">
-        <v>0.2825800000000001</v>
+        <v>-0.04883532800000007</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2303939999792332</v>
+        <v>0.2364188347589816</v>
       </c>
       <c r="T52">
-        <v>2.21138855440637</v>
+        <v>2.28356452261565</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.27</v>
+        <v>0.2443774727731333</v>
       </c>
       <c r="W52">
-        <v>0.06569999999999999</v>
+        <v>0.110925386996904</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.505847953216374</v>
+        <v>0.9051017510116048</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.172417176400322</v>
+        <v>0.173427176400322</v>
       </c>
       <c r="C53">
-        <v>5.304155962571582</v>
+        <v>5.061258256852472</v>
       </c>
       <c r="D53">
-        <v>11.48615596257158</v>
+        <v>11.39525825685247</v>
       </c>
       <c r="E53">
-        <v>7.752</v>
+        <v>7.904</v>
       </c>
       <c r="F53">
-        <v>7.752</v>
+        <v>7.904</v>
       </c>
       <c r="G53">
         <v>1.57</v>
@@ -5633,37 +5633,37 @@
         <v>1.03</v>
       </c>
       <c r="M53">
-        <v>1.1379936</v>
+        <v>1.1603072</v>
       </c>
       <c r="N53">
-        <v>-0.1079936000000001</v>
+        <v>-0.1303072000000001</v>
       </c>
       <c r="O53">
-        <v>-0.02915827200000004</v>
+        <v>-0.03518294400000002</v>
       </c>
       <c r="P53">
-        <v>-0.07883532800000009</v>
+        <v>-0.09512425600000005</v>
       </c>
       <c r="Q53">
-        <v>-0.04883532800000007</v>
+        <v>-0.06512425600000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2364188347589816</v>
+        <v>0.2403900604831271</v>
       </c>
       <c r="T53">
-        <v>2.28356452261565</v>
+        <v>2.331138783503476</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2443774727731333</v>
+        <v>0.2396779059890346</v>
       </c>
       <c r="W53">
-        <v>0.110925386996904</v>
+        <v>0.1116152834008097</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9051017510116048</v>
+        <v>0.8876959481075356</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.173427176400322</v>
+        <v>0.174437176400322</v>
       </c>
       <c r="C54">
-        <v>5.061258256852472</v>
+        <v>4.819787925168546</v>
       </c>
       <c r="D54">
-        <v>11.39525825685247</v>
+        <v>11.30578792516854</v>
       </c>
       <c r="E54">
-        <v>7.904</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="F54">
-        <v>7.904</v>
+        <v>8.055999999999999</v>
       </c>
       <c r="G54">
         <v>1.57</v>
@@ -5715,37 +5715,37 @@
         <v>1.03</v>
       </c>
       <c r="M54">
-        <v>1.1603072</v>
+        <v>1.1826208</v>
       </c>
       <c r="N54">
-        <v>-0.1303072000000001</v>
+        <v>-0.1526208</v>
       </c>
       <c r="O54">
-        <v>-0.03518294400000002</v>
+        <v>-0.041207616</v>
       </c>
       <c r="P54">
-        <v>-0.09512425600000005</v>
+        <v>-0.111413184</v>
       </c>
       <c r="Q54">
-        <v>-0.06512425600000002</v>
+        <v>-0.08141318399999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2403900604831271</v>
+        <v>0.2445302745359595</v>
       </c>
       <c r="T54">
-        <v>2.331138783503476</v>
+        <v>2.380737481024827</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2396779059890346</v>
+        <v>0.2351556813477321</v>
       </c>
       <c r="W54">
-        <v>0.1116152834008097</v>
+        <v>0.1122791459781529</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8876959481075356</v>
+        <v>0.8709469679545633</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.174437176400322</v>
+        <v>0.175447176400322</v>
       </c>
       <c r="C55">
-        <v>4.819787925168546</v>
+        <v>4.57971160818682</v>
       </c>
       <c r="D55">
-        <v>11.30578792516854</v>
+        <v>11.21771160818682</v>
       </c>
       <c r="E55">
-        <v>8.055999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="F55">
-        <v>8.055999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="G55">
         <v>1.57</v>
@@ -5797,37 +5797,37 @@
         <v>1.03</v>
       </c>
       <c r="M55">
-        <v>1.1826208</v>
+        <v>1.2049344</v>
       </c>
       <c r="N55">
-        <v>-0.1526208</v>
+        <v>-0.1749344000000002</v>
       </c>
       <c r="O55">
-        <v>-0.041207616</v>
+        <v>-0.04723228800000005</v>
       </c>
       <c r="P55">
-        <v>-0.111413184</v>
+        <v>-0.1277021120000001</v>
       </c>
       <c r="Q55">
-        <v>-0.08141318399999997</v>
+        <v>-0.09770211200000009</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2445302745359595</v>
+        <v>0.2488504978954369</v>
       </c>
       <c r="T55">
-        <v>2.380737481024827</v>
+        <v>2.432492643655801</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2351556813477321</v>
+        <v>0.2308009465079593</v>
       </c>
       <c r="W55">
-        <v>0.1122791459781529</v>
+        <v>0.1129184210526316</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8709469679545633</v>
+        <v>0.8548183203998491</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.175447176400322</v>
+        <v>0.176457176400322</v>
       </c>
       <c r="C56">
-        <v>4.57971160818682</v>
+        <v>4.340996978065355</v>
       </c>
       <c r="D56">
-        <v>11.21771160818682</v>
+        <v>11.13099697806535</v>
       </c>
       <c r="E56">
-        <v>8.208</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F56">
-        <v>8.208</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G56">
         <v>1.57</v>
@@ -5879,37 +5879,37 @@
         <v>1.03</v>
       </c>
       <c r="M56">
-        <v>1.2049344</v>
+        <v>1.227248</v>
       </c>
       <c r="N56">
-        <v>-0.1749344000000002</v>
+        <v>-0.1972480000000001</v>
       </c>
       <c r="O56">
-        <v>-0.04723228800000005</v>
+        <v>-0.05325696000000003</v>
       </c>
       <c r="P56">
-        <v>-0.1277021120000001</v>
+        <v>-0.1439910400000001</v>
       </c>
       <c r="Q56">
-        <v>-0.09770211200000009</v>
+        <v>-0.11399104</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2488504978954369</v>
+        <v>0.2533627311820022</v>
       </c>
       <c r="T56">
-        <v>2.432492643655801</v>
+        <v>2.486548035737041</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2308009465079593</v>
+        <v>0.22660456566236</v>
       </c>
       <c r="W56">
-        <v>0.1129184210526316</v>
+        <v>0.1135344497607656</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8548183203998491</v>
+        <v>0.8392761691198518</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.176457176400322</v>
+        <v>0.1774671764003221</v>
       </c>
       <c r="C57">
-        <v>4.340996978065355</v>
+        <v>4.103612698891137</v>
       </c>
       <c r="D57">
-        <v>11.13099697806535</v>
+        <v>11.04561269889114</v>
       </c>
       <c r="E57">
-        <v>8.359999999999999</v>
+        <v>8.512</v>
       </c>
       <c r="F57">
-        <v>8.359999999999999</v>
+        <v>8.512</v>
       </c>
       <c r="G57">
         <v>1.57</v>
@@ -5961,37 +5961,37 @@
         <v>1.03</v>
       </c>
       <c r="M57">
-        <v>1.227248</v>
+        <v>1.2495616</v>
       </c>
       <c r="N57">
-        <v>-0.1972480000000001</v>
+        <v>-0.2195616000000002</v>
       </c>
       <c r="O57">
-        <v>-0.05325696000000003</v>
+        <v>-0.05928163200000007</v>
       </c>
       <c r="P57">
-        <v>-0.1439910400000001</v>
+        <v>-0.1602799680000002</v>
       </c>
       <c r="Q57">
-        <v>-0.11399104</v>
+        <v>-0.1302799680000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2533627311820022</v>
+        <v>0.2580800659815932</v>
       </c>
       <c r="T57">
-        <v>2.486548035737041</v>
+        <v>2.543060491094701</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.22660456566236</v>
+        <v>0.2225580555612464</v>
       </c>
       <c r="W57">
-        <v>0.1135344497607656</v>
+        <v>0.114128477443609</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8392761691198518</v>
+        <v>0.824289094671283</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1774671764003221</v>
+        <v>0.178477176400322</v>
       </c>
       <c r="C58">
-        <v>4.103612698891137</v>
+        <v>3.867528388924974</v>
       </c>
       <c r="D58">
-        <v>11.04561269889114</v>
+        <v>10.96152838892497</v>
       </c>
       <c r="E58">
-        <v>8.512</v>
+        <v>8.664</v>
       </c>
       <c r="F58">
-        <v>8.512</v>
+        <v>8.664</v>
       </c>
       <c r="G58">
         <v>1.57</v>
@@ -6043,37 +6043,37 @@
         <v>1.03</v>
       </c>
       <c r="M58">
-        <v>1.2495616</v>
+        <v>1.2718752</v>
       </c>
       <c r="N58">
-        <v>-0.2195616000000002</v>
+        <v>-0.2418752</v>
       </c>
       <c r="O58">
-        <v>-0.05928163200000007</v>
+        <v>-0.065306304</v>
       </c>
       <c r="P58">
-        <v>-0.1602799680000002</v>
+        <v>-0.176568896</v>
       </c>
       <c r="Q58">
-        <v>-0.1302799680000001</v>
+        <v>-0.1465688959999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2580800659815932</v>
+        <v>0.2630168117020953</v>
       </c>
       <c r="T58">
-        <v>2.543060491094701</v>
+        <v>2.602201432748067</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2225580555612464</v>
+        <v>0.2186535282706983</v>
       </c>
       <c r="W58">
-        <v>0.114128477443609</v>
+        <v>0.1147016620498615</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.824289094671283</v>
+        <v>0.8098278824840677</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.178477176400322</v>
+        <v>0.2143834676017545</v>
       </c>
       <c r="C59">
-        <v>3.867528388924974</v>
+        <v>1.380852065412142</v>
       </c>
       <c r="D59">
-        <v>10.96152838892497</v>
+        <v>8.626852065412143</v>
       </c>
       <c r="E59">
-        <v>8.664</v>
+        <v>8.816000000000001</v>
       </c>
       <c r="F59">
-        <v>8.664</v>
+        <v>8.816000000000001</v>
       </c>
       <c r="G59">
         <v>1.57</v>
@@ -6125,45 +6125,45 @@
         <v>1.03</v>
       </c>
       <c r="M59">
-        <v>1.2718752</v>
+        <v>1.7702528</v>
       </c>
       <c r="N59">
-        <v>-0.2418752</v>
+        <v>-0.7402528000000002</v>
       </c>
       <c r="O59">
-        <v>-0.065306304</v>
+        <v>-0.199868256</v>
       </c>
       <c r="P59">
-        <v>-0.176568896</v>
+        <v>-0.5403845440000001</v>
       </c>
       <c r="Q59">
-        <v>-0.1465688959999999</v>
+        <v>-0.5103845440000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2630168117020953</v>
+        <v>0.2767036196031749</v>
       </c>
       <c r="T59">
-        <v>2.602201432748067</v>
+        <v>2.766165864648404</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.2186535282706983</v>
+        <v>0.1570962068242457</v>
       </c>
       <c r="W59">
-        <v>0.1147016620498615</v>
+        <v>0.1692550816696915</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8098278824840677</v>
+        <v>0.5818378030527617</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2143834676017544</v>
+        <v>0.2159334676017544</v>
       </c>
       <c r="C60">
-        <v>1.380852065412146</v>
+        <v>1.15025717817521</v>
       </c>
       <c r="D60">
-        <v>8.626852065412145</v>
+        <v>8.548257178175209</v>
       </c>
       <c r="E60">
-        <v>8.815999999999999</v>
+        <v>8.968</v>
       </c>
       <c r="F60">
-        <v>8.815999999999999</v>
+        <v>8.968</v>
       </c>
       <c r="G60">
         <v>1.57</v>
@@ -6207,37 +6207,37 @@
         <v>1.03</v>
       </c>
       <c r="M60">
-        <v>1.7702528</v>
+        <v>1.8007744</v>
       </c>
       <c r="N60">
-        <v>-0.7402527999999997</v>
+        <v>-0.7707744000000001</v>
       </c>
       <c r="O60">
-        <v>-0.1998682559999999</v>
+        <v>-0.208109088</v>
       </c>
       <c r="P60">
-        <v>-0.5403845439999998</v>
+        <v>-0.562665312</v>
       </c>
       <c r="Q60">
-        <v>-0.5103845439999998</v>
+        <v>-0.532665312</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2767036196031747</v>
+        <v>0.2823354152032522</v>
       </c>
       <c r="T60">
-        <v>2.766165864648403</v>
+        <v>2.833633324761779</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1570962068242457</v>
+        <v>0.1544335592509534</v>
       </c>
       <c r="W60">
-        <v>0.1692550816696915</v>
+        <v>0.1697897413024086</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5818378030527618</v>
+        <v>0.5719761453739014</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2159334676017544</v>
+        <v>0.2174834676017545</v>
       </c>
       <c r="C61">
-        <v>1.15025717817521</v>
+        <v>0.9210814383601988</v>
       </c>
       <c r="D61">
-        <v>8.548257178175209</v>
+        <v>8.471081438360198</v>
       </c>
       <c r="E61">
-        <v>8.968</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F61">
-        <v>8.968</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G61">
         <v>1.57</v>
@@ -6289,37 +6289,37 @@
         <v>1.03</v>
       </c>
       <c r="M61">
-        <v>1.8007744</v>
+        <v>1.831296</v>
       </c>
       <c r="N61">
-        <v>-0.7707744000000001</v>
+        <v>-0.8012959999999998</v>
       </c>
       <c r="O61">
-        <v>-0.208109088</v>
+        <v>-0.2163499199999999</v>
       </c>
       <c r="P61">
-        <v>-0.562665312</v>
+        <v>-0.5849460799999998</v>
       </c>
       <c r="Q61">
-        <v>-0.532665312</v>
+        <v>-0.5549460799999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2823354152032522</v>
+        <v>0.2882488005833335</v>
       </c>
       <c r="T61">
-        <v>2.833633324761779</v>
+        <v>2.904474157880823</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1544335592509534</v>
+        <v>0.1518596665967708</v>
       </c>
       <c r="W61">
-        <v>0.1697897413024086</v>
+        <v>0.1703065789473684</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5719761453739014</v>
+        <v>0.5624432096176697</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2174834676017545</v>
+        <v>0.2190334676017545</v>
       </c>
       <c r="C62">
-        <v>0.9210814383601988</v>
+        <v>0.6932867526609936</v>
       </c>
       <c r="D62">
-        <v>8.471081438360198</v>
+        <v>8.395286752660994</v>
       </c>
       <c r="E62">
-        <v>9.119999999999999</v>
+        <v>9.272</v>
       </c>
       <c r="F62">
-        <v>9.119999999999999</v>
+        <v>9.272</v>
       </c>
       <c r="G62">
         <v>1.57</v>
@@ -6371,37 +6371,37 @@
         <v>1.03</v>
       </c>
       <c r="M62">
-        <v>1.831296</v>
+        <v>1.8618176</v>
       </c>
       <c r="N62">
-        <v>-0.8012959999999998</v>
+        <v>-0.8318176000000002</v>
       </c>
       <c r="O62">
-        <v>-0.2163499199999999</v>
+        <v>-0.2245907520000001</v>
       </c>
       <c r="P62">
-        <v>-0.5849460799999998</v>
+        <v>-0.607226848</v>
       </c>
       <c r="Q62">
-        <v>-0.5549460799999998</v>
+        <v>-0.577226848</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2882488005833335</v>
+        <v>0.2944654364957267</v>
       </c>
       <c r="T62">
-        <v>2.904474157880823</v>
+        <v>2.978947854236742</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1518596665967708</v>
+        <v>0.1493701638656762</v>
       </c>
       <c r="W62">
-        <v>0.1703065789473684</v>
+        <v>0.1708064710957722</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5624432096176697</v>
+        <v>0.5532228291321341</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2190334676017545</v>
+        <v>0.2205834676017545</v>
       </c>
       <c r="C63">
-        <v>0.6932867526609936</v>
+        <v>0.4668363790348433</v>
       </c>
       <c r="D63">
-        <v>8.395286752660994</v>
+        <v>8.320836379034843</v>
       </c>
       <c r="E63">
-        <v>9.272</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="F63">
-        <v>9.272</v>
+        <v>9.423999999999999</v>
       </c>
       <c r="G63">
         <v>1.57</v>
@@ -6453,37 +6453,37 @@
         <v>1.03</v>
       </c>
       <c r="M63">
-        <v>1.8618176</v>
+        <v>1.8923392</v>
       </c>
       <c r="N63">
-        <v>-0.8318176000000002</v>
+        <v>-0.8623391999999999</v>
       </c>
       <c r="O63">
-        <v>-0.2245907520000001</v>
+        <v>-0.232831584</v>
       </c>
       <c r="P63">
-        <v>-0.607226848</v>
+        <v>-0.6295076159999999</v>
       </c>
       <c r="Q63">
-        <v>-0.577226848</v>
+        <v>-0.5995076159999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2944654364957267</v>
+        <v>0.30100926377193</v>
       </c>
       <c r="T63">
-        <v>2.978947854236742</v>
+        <v>3.05734121882192</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1493701638656762</v>
+        <v>0.1469609676742944</v>
       </c>
       <c r="W63">
-        <v>0.1708064710957722</v>
+        <v>0.1712902376910017</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5532228291321341</v>
+        <v>0.5442998802751642</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2205834676017545</v>
+        <v>0.2221334676017545</v>
       </c>
       <c r="C64">
-        <v>0.4668363790348433</v>
+        <v>0.2416948673132477</v>
       </c>
       <c r="D64">
-        <v>8.320836379034843</v>
+        <v>8.247694867313246</v>
       </c>
       <c r="E64">
-        <v>9.423999999999999</v>
+        <v>9.575999999999999</v>
       </c>
       <c r="F64">
-        <v>9.423999999999999</v>
+        <v>9.575999999999999</v>
       </c>
       <c r="G64">
         <v>1.57</v>
@@ -6535,37 +6535,37 @@
         <v>1.03</v>
       </c>
       <c r="M64">
-        <v>1.8923392</v>
+        <v>1.9228608</v>
       </c>
       <c r="N64">
-        <v>-0.8623391999999999</v>
+        <v>-0.8928607999999998</v>
       </c>
       <c r="O64">
-        <v>-0.232831584</v>
+        <v>-0.241072416</v>
       </c>
       <c r="P64">
-        <v>-0.6295076159999999</v>
+        <v>-0.6517883839999998</v>
       </c>
       <c r="Q64">
-        <v>-0.5995076159999999</v>
+        <v>-0.6217883839999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.30100926377193</v>
+        <v>0.3079068114414416</v>
       </c>
       <c r="T64">
-        <v>3.05734121882192</v>
+        <v>3.139972062573863</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1469609676742944</v>
+        <v>0.1446282539016865</v>
       </c>
       <c r="W64">
-        <v>0.1712902376910017</v>
+        <v>0.1717586466165414</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5442998802751642</v>
+        <v>0.535660199635876</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2221334676017545</v>
+        <v>0.2236834676017544</v>
       </c>
       <c r="C65">
-        <v>0.2416948673132477</v>
+        <v>0.01782800291775288</v>
       </c>
       <c r="D65">
-        <v>8.247694867313246</v>
+        <v>8.175828002917752</v>
       </c>
       <c r="E65">
-        <v>9.575999999999999</v>
+        <v>9.728</v>
       </c>
       <c r="F65">
-        <v>9.575999999999999</v>
+        <v>9.728</v>
       </c>
       <c r="G65">
         <v>1.57</v>
@@ -6617,37 +6617,37 @@
         <v>1.03</v>
       </c>
       <c r="M65">
-        <v>1.9228608</v>
+        <v>1.9533824</v>
       </c>
       <c r="N65">
-        <v>-0.8928607999999998</v>
+        <v>-0.9233823999999999</v>
       </c>
       <c r="O65">
-        <v>-0.241072416</v>
+        <v>-0.249313248</v>
       </c>
       <c r="P65">
-        <v>-0.6517883839999998</v>
+        <v>-0.6740691519999999</v>
       </c>
       <c r="Q65">
-        <v>-0.6217883839999998</v>
+        <v>-0.6440691519999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3079068114414416</v>
+        <v>0.315187556203704</v>
       </c>
       <c r="T65">
-        <v>3.139972062573863</v>
+        <v>3.227193508756471</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1446282539016865</v>
+        <v>0.1423684374344727</v>
       </c>
       <c r="W65">
-        <v>0.1717586466165414</v>
+        <v>0.1722124177631579</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.535660199635876</v>
+        <v>0.5272905090165654</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2236834676017544</v>
+        <v>0.2252334676017544</v>
       </c>
       <c r="C66">
-        <v>0.01782800291775288</v>
+        <v>-0.2047972465070025</v>
       </c>
       <c r="D66">
-        <v>8.175828002917752</v>
+        <v>8.105202753492996</v>
       </c>
       <c r="E66">
-        <v>9.728</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="F66">
-        <v>9.728</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="G66">
         <v>1.57</v>
@@ -6699,37 +6699,37 @@
         <v>1.03</v>
       </c>
       <c r="M66">
-        <v>1.9533824</v>
+        <v>1.983904</v>
       </c>
       <c r="N66">
-        <v>-0.9233823999999999</v>
+        <v>-0.9539039999999999</v>
       </c>
       <c r="O66">
-        <v>-0.249313248</v>
+        <v>-0.25755408</v>
       </c>
       <c r="P66">
-        <v>-0.6740691519999999</v>
+        <v>-0.6963499199999998</v>
       </c>
       <c r="Q66">
-        <v>-0.6440691519999999</v>
+        <v>-0.6663499199999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.315187556203704</v>
+        <v>0.3228843435238097</v>
       </c>
       <c r="T66">
-        <v>3.227193508756471</v>
+        <v>3.319399037578084</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1423684374344727</v>
+        <v>0.1401781537816346</v>
       </c>
       <c r="W66">
-        <v>0.1722124177631579</v>
+        <v>0.1726522267206478</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5272905090165654</v>
+        <v>0.5191783473393874</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2252334676017544</v>
+        <v>0.2267834676017545</v>
       </c>
       <c r="C67">
-        <v>-0.2047972465070025</v>
+        <v>-0.4262127817179806</v>
       </c>
       <c r="D67">
-        <v>8.105202753492996</v>
+        <v>8.035787218282019</v>
       </c>
       <c r="E67">
-        <v>9.879999999999999</v>
+        <v>10.032</v>
       </c>
       <c r="F67">
-        <v>9.879999999999999</v>
+        <v>10.032</v>
       </c>
       <c r="G67">
         <v>1.57</v>
@@ -6781,37 +6781,37 @@
         <v>1.03</v>
       </c>
       <c r="M67">
-        <v>1.983904</v>
+        <v>2.0144256</v>
       </c>
       <c r="N67">
-        <v>-0.9539039999999999</v>
+        <v>-0.9844256</v>
       </c>
       <c r="O67">
-        <v>-0.25755408</v>
+        <v>-0.265794912</v>
       </c>
       <c r="P67">
-        <v>-0.6963499199999998</v>
+        <v>-0.718630688</v>
       </c>
       <c r="Q67">
-        <v>-0.6663499199999998</v>
+        <v>-0.6886306879999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3228843435238097</v>
+        <v>0.331033883039216</v>
       </c>
       <c r="T67">
-        <v>3.319399037578084</v>
+        <v>3.417028421036263</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1401781537816346</v>
+        <v>0.1380542423607007</v>
       </c>
       <c r="W67">
-        <v>0.1726522267206478</v>
+        <v>0.1730787081339713</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5191783473393874</v>
+        <v>0.511312008743336</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2267834676017545</v>
+        <v>0.2283334676017545</v>
       </c>
       <c r="C68">
-        <v>-0.4262127817179806</v>
+        <v>-0.6464494199191009</v>
       </c>
       <c r="D68">
-        <v>8.035787218282019</v>
+        <v>7.967550580080898</v>
       </c>
       <c r="E68">
-        <v>10.032</v>
+        <v>10.184</v>
       </c>
       <c r="F68">
-        <v>10.032</v>
+        <v>10.184</v>
       </c>
       <c r="G68">
         <v>1.57</v>
@@ -6863,37 +6863,37 @@
         <v>1.03</v>
       </c>
       <c r="M68">
-        <v>2.0144256</v>
+        <v>2.0449472</v>
       </c>
       <c r="N68">
-        <v>-0.9844256</v>
+        <v>-1.0149472</v>
       </c>
       <c r="O68">
-        <v>-0.265794912</v>
+        <v>-0.2740357439999999</v>
       </c>
       <c r="P68">
-        <v>-0.718630688</v>
+        <v>-0.7409114559999999</v>
       </c>
       <c r="Q68">
-        <v>-0.6886306879999999</v>
+        <v>-0.7109114559999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.331033883039216</v>
+        <v>0.3396773340404043</v>
       </c>
       <c r="T68">
-        <v>3.417028421036263</v>
+        <v>3.520574736825241</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1380542423607007</v>
+        <v>0.1359937312806903</v>
       </c>
       <c r="W68">
-        <v>0.1730787081339713</v>
+        <v>0.1734924587588374</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.511312008743336</v>
+        <v>0.5036804862247789</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2283334676017545</v>
+        <v>0.2551265442983398</v>
       </c>
       <c r="C69">
-        <v>-0.6464494199191009</v>
+        <v>-1.818268451908555</v>
       </c>
       <c r="D69">
-        <v>7.967550580080898</v>
+        <v>6.947731548091445</v>
       </c>
       <c r="E69">
-        <v>10.184</v>
+        <v>10.336</v>
       </c>
       <c r="F69">
-        <v>10.184</v>
+        <v>10.336</v>
       </c>
       <c r="G69">
         <v>1.57</v>
@@ -6945,45 +6945,45 @@
         <v>1.03</v>
       </c>
       <c r="M69">
-        <v>2.0449472</v>
+        <v>2.4372288</v>
       </c>
       <c r="N69">
-        <v>-1.0149472</v>
+        <v>-1.4072288</v>
       </c>
       <c r="O69">
-        <v>-0.2740357439999999</v>
+        <v>-0.3799517760000001</v>
       </c>
       <c r="P69">
-        <v>-0.7409114559999999</v>
+        <v>-1.027277024</v>
       </c>
       <c r="Q69">
-        <v>-0.7109114559999998</v>
+        <v>-0.997277024</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3396773340404043</v>
+        <v>0.353370615405996</v>
       </c>
       <c r="T69">
-        <v>3.520574736825241</v>
+        <v>3.684616719162381</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1359937312806903</v>
+        <v>0.1141050031905088</v>
       </c>
       <c r="W69">
-        <v>0.1734924587588374</v>
+        <v>0.208894040247678</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5036804862247789</v>
+        <v>0.4226111229278104</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2551265442983398</v>
+        <v>0.2570265442983398</v>
       </c>
       <c r="C70">
-        <v>-1.818268451908555</v>
+        <v>-2.032763864051118</v>
       </c>
       <c r="D70">
-        <v>6.947731548091445</v>
+        <v>6.885236135948881</v>
       </c>
       <c r="E70">
-        <v>10.336</v>
+        <v>10.488</v>
       </c>
       <c r="F70">
-        <v>10.336</v>
+        <v>10.488</v>
       </c>
       <c r="G70">
         <v>1.57</v>
@@ -7027,37 +7027,37 @@
         <v>1.03</v>
       </c>
       <c r="M70">
-        <v>2.4372288</v>
+        <v>2.4730704</v>
       </c>
       <c r="N70">
-        <v>-1.4072288</v>
+        <v>-1.4430704</v>
       </c>
       <c r="O70">
-        <v>-0.3799517760000001</v>
+        <v>-0.3896290080000001</v>
       </c>
       <c r="P70">
-        <v>-1.027277024</v>
+        <v>-1.053441392</v>
       </c>
       <c r="Q70">
-        <v>-0.997277024</v>
+        <v>-1.023441392</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.353370615405996</v>
+        <v>0.3632922481610282</v>
       </c>
       <c r="T70">
-        <v>3.684616719162381</v>
+        <v>3.803475323006329</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1141050031905088</v>
+        <v>0.1124513074920957</v>
       </c>
       <c r="W70">
-        <v>0.208894040247678</v>
+        <v>0.2092839816933638</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4226111229278104</v>
+        <v>0.4164863240447987</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2570265442983398</v>
+        <v>0.2589265442983398</v>
       </c>
       <c r="C71">
-        <v>-2.032763864051118</v>
+        <v>-2.246144996567349</v>
       </c>
       <c r="D71">
-        <v>6.885236135948881</v>
+        <v>6.823855003432652</v>
       </c>
       <c r="E71">
-        <v>10.488</v>
+        <v>10.64</v>
       </c>
       <c r="F71">
-        <v>10.488</v>
+        <v>10.64</v>
       </c>
       <c r="G71">
         <v>1.57</v>
@@ -7109,37 +7109,37 @@
         <v>1.03</v>
       </c>
       <c r="M71">
-        <v>2.4730704</v>
+        <v>2.508912</v>
       </c>
       <c r="N71">
-        <v>-1.4430704</v>
+        <v>-1.478912</v>
       </c>
       <c r="O71">
-        <v>-0.3896290080000001</v>
+        <v>-0.39930624</v>
       </c>
       <c r="P71">
-        <v>-1.053441392</v>
+        <v>-1.07960576</v>
       </c>
       <c r="Q71">
-        <v>-1.023441392</v>
+        <v>-1.04960576</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3632922481610282</v>
+        <v>0.373875323099729</v>
       </c>
       <c r="T71">
-        <v>3.803475323006329</v>
+        <v>3.930257833773207</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1124513074920957</v>
+        <v>0.1108448602422086</v>
       </c>
       <c r="W71">
-        <v>0.2092839816933638</v>
+        <v>0.2096627819548872</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4164863240447987</v>
+        <v>0.4105365194155873</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2589265442983398</v>
+        <v>0.2608265442983397</v>
       </c>
       <c r="C72">
-        <v>-2.246144996567349</v>
+        <v>-2.458441387177304</v>
       </c>
       <c r="D72">
-        <v>6.823855003432652</v>
+        <v>6.763558612822696</v>
       </c>
       <c r="E72">
-        <v>10.64</v>
+        <v>10.792</v>
       </c>
       <c r="F72">
-        <v>10.64</v>
+        <v>10.792</v>
       </c>
       <c r="G72">
         <v>1.57</v>
@@ -7191,37 +7191,37 @@
         <v>1.03</v>
       </c>
       <c r="M72">
-        <v>2.508912</v>
+        <v>2.5447536</v>
       </c>
       <c r="N72">
-        <v>-1.478912</v>
+        <v>-1.5147536</v>
       </c>
       <c r="O72">
-        <v>-0.39930624</v>
+        <v>-0.408983472</v>
       </c>
       <c r="P72">
-        <v>-1.07960576</v>
+        <v>-1.105770128</v>
       </c>
       <c r="Q72">
-        <v>-1.04960576</v>
+        <v>-1.075770128</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.373875323099729</v>
+        <v>0.3851882652755818</v>
       </c>
       <c r="T72">
-        <v>3.930257833773207</v>
+        <v>4.065783965972283</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1108448602422086</v>
+        <v>0.1092836650275296</v>
       </c>
       <c r="W72">
-        <v>0.2096627819548872</v>
+        <v>0.2100309117865085</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4105365194155873</v>
+        <v>0.4047543149167763</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2608265442983397</v>
+        <v>0.2627265442983397</v>
       </c>
       <c r="C73">
-        <v>-2.458441387177304</v>
+        <v>-2.669681538749947</v>
       </c>
       <c r="D73">
-        <v>6.763558612822696</v>
+        <v>6.704318461250053</v>
       </c>
       <c r="E73">
-        <v>10.792</v>
+        <v>10.944</v>
       </c>
       <c r="F73">
-        <v>10.792</v>
+        <v>10.944</v>
       </c>
       <c r="G73">
         <v>1.57</v>
@@ -7273,37 +7273,37 @@
         <v>1.03</v>
       </c>
       <c r="M73">
-        <v>2.5447536</v>
+        <v>2.5805952</v>
       </c>
       <c r="N73">
-        <v>-1.5147536</v>
+        <v>-1.5505952</v>
       </c>
       <c r="O73">
-        <v>-0.408983472</v>
+        <v>-0.418660704</v>
       </c>
       <c r="P73">
-        <v>-1.105770128</v>
+        <v>-1.131934496</v>
       </c>
       <c r="Q73">
-        <v>-1.075770128</v>
+        <v>-1.101934496</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3851882652755817</v>
+        <v>0.3973092747497097</v>
       </c>
       <c r="T73">
-        <v>4.065783965972281</v>
+        <v>4.210990536185578</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1092836650275296</v>
+        <v>0.1077658363465917</v>
       </c>
       <c r="W73">
-        <v>0.2100309117865085</v>
+        <v>0.2103888157894737</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4047543149167763</v>
+        <v>0.3991327272095988</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2627265442983397</v>
+        <v>0.2646265442983398</v>
       </c>
       <c r="C74">
-        <v>-2.669681538749947</v>
+        <v>-2.879892964229519</v>
       </c>
       <c r="D74">
-        <v>6.704318461250053</v>
+        <v>6.646107035770481</v>
       </c>
       <c r="E74">
-        <v>10.944</v>
+        <v>11.096</v>
       </c>
       <c r="F74">
-        <v>10.944</v>
+        <v>11.096</v>
       </c>
       <c r="G74">
         <v>1.57</v>
@@ -7355,37 +7355,37 @@
         <v>1.03</v>
       </c>
       <c r="M74">
-        <v>2.5805952</v>
+        <v>2.6164368</v>
       </c>
       <c r="N74">
-        <v>-1.5505952</v>
+        <v>-1.5864368</v>
       </c>
       <c r="O74">
-        <v>-0.418660704</v>
+        <v>-0.4283379360000001</v>
       </c>
       <c r="P74">
-        <v>-1.131934496</v>
+        <v>-1.158098864</v>
       </c>
       <c r="Q74">
-        <v>-1.101934496</v>
+        <v>-1.128098864</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3973092747497097</v>
+        <v>0.4103281367774766</v>
       </c>
       <c r="T74">
-        <v>4.210990536185578</v>
+        <v>4.366953148636895</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1077658363465917</v>
+        <v>0.1062895920130767</v>
       </c>
       <c r="W74">
-        <v>0.2103888157894737</v>
+        <v>0.2107369142033165</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3991327272095988</v>
+        <v>0.3936651556039878</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2646265442983398</v>
+        <v>0.2665265442983398</v>
       </c>
       <c r="C75">
-        <v>-2.879892964229519</v>
+        <v>-3.089102229241597</v>
       </c>
       <c r="D75">
-        <v>6.646107035770481</v>
+        <v>6.588897770758402</v>
       </c>
       <c r="E75">
-        <v>11.096</v>
+        <v>11.248</v>
       </c>
       <c r="F75">
-        <v>11.096</v>
+        <v>11.248</v>
       </c>
       <c r="G75">
         <v>1.57</v>
@@ -7437,37 +7437,37 @@
         <v>1.03</v>
       </c>
       <c r="M75">
-        <v>2.6164368</v>
+        <v>2.6522784</v>
       </c>
       <c r="N75">
-        <v>-1.5864368</v>
+        <v>-1.6222784</v>
       </c>
       <c r="O75">
-        <v>-0.4283379360000001</v>
+        <v>-0.4380151680000001</v>
       </c>
       <c r="P75">
-        <v>-1.158098864</v>
+        <v>-1.184263232</v>
       </c>
       <c r="Q75">
-        <v>-1.128098864</v>
+        <v>-1.154263232</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4103281367774766</v>
+        <v>0.4243484497304565</v>
       </c>
       <c r="T75">
-        <v>4.366953148636895</v>
+        <v>4.53491288512293</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1062895920130767</v>
+        <v>0.1048532461750622</v>
       </c>
       <c r="W75">
-        <v>0.2107369142033165</v>
+        <v>0.2110756045519203</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3936651556039878</v>
+        <v>0.388345356203934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2665265442983398</v>
+        <v>0.2684265442983397</v>
       </c>
       <c r="C76">
-        <v>-3.089102229241597</v>
+        <v>-3.29733499251741</v>
       </c>
       <c r="D76">
-        <v>6.588897770758402</v>
+        <v>6.532665007482589</v>
       </c>
       <c r="E76">
-        <v>11.248</v>
+        <v>11.4</v>
       </c>
       <c r="F76">
-        <v>11.248</v>
+        <v>11.4</v>
       </c>
       <c r="G76">
         <v>1.57</v>
@@ -7519,37 +7519,37 @@
         <v>1.03</v>
       </c>
       <c r="M76">
-        <v>2.6522784</v>
+        <v>2.68812</v>
       </c>
       <c r="N76">
-        <v>-1.6222784</v>
+        <v>-1.65812</v>
       </c>
       <c r="O76">
-        <v>-0.4380151680000001</v>
+        <v>-0.4476923999999999</v>
       </c>
       <c r="P76">
-        <v>-1.184263232</v>
+        <v>-1.2104276</v>
       </c>
       <c r="Q76">
-        <v>-1.154263232</v>
+        <v>-1.1804276</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4243484497304565</v>
+        <v>0.4394903877196748</v>
       </c>
       <c r="T76">
-        <v>4.53491288512293</v>
+        <v>4.716309400527847</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1048532461750622</v>
+        <v>0.103455202892728</v>
       </c>
       <c r="W76">
-        <v>0.2110756045519203</v>
+        <v>0.2114052631578947</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.388345356203934</v>
+        <v>0.3831674181212149</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2684265442983397</v>
+        <v>0.2703265442983398</v>
       </c>
       <c r="C77">
-        <v>-3.29733499251741</v>
+        <v>-3.504616044265683</v>
       </c>
       <c r="D77">
-        <v>6.532665007482589</v>
+        <v>6.477383955734317</v>
       </c>
       <c r="E77">
-        <v>11.4</v>
+        <v>11.552</v>
       </c>
       <c r="F77">
-        <v>11.4</v>
+        <v>11.552</v>
       </c>
       <c r="G77">
         <v>1.57</v>
@@ -7601,37 +7601,37 @@
         <v>1.03</v>
       </c>
       <c r="M77">
-        <v>2.68812</v>
+        <v>2.7239616</v>
       </c>
       <c r="N77">
-        <v>-1.65812</v>
+        <v>-1.6939616</v>
       </c>
       <c r="O77">
-        <v>-0.4476923999999999</v>
+        <v>-0.457369632</v>
       </c>
       <c r="P77">
-        <v>-1.2104276</v>
+        <v>-1.236591968</v>
       </c>
       <c r="Q77">
-        <v>-1.1804276</v>
+        <v>-1.206591968</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4394903877196748</v>
+        <v>0.4558941538746613</v>
       </c>
       <c r="T77">
-        <v>4.716309400527847</v>
+        <v>4.912822292216508</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.103455202892728</v>
+        <v>0.1020939502230868</v>
       </c>
       <c r="W77">
-        <v>0.2114052631578947</v>
+        <v>0.2117262465373961</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3831674181212149</v>
+        <v>0.3781257415669883</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2703265442983398</v>
+        <v>0.2722265442983398</v>
       </c>
       <c r="C78">
-        <v>-3.504616044265683</v>
+        <v>-3.710969342612535</v>
       </c>
       <c r="D78">
-        <v>6.477383955734317</v>
+        <v>6.423030657387463</v>
       </c>
       <c r="E78">
-        <v>11.552</v>
+        <v>11.704</v>
       </c>
       <c r="F78">
-        <v>11.552</v>
+        <v>11.704</v>
       </c>
       <c r="G78">
         <v>1.57</v>
@@ -7683,37 +7683,37 @@
         <v>1.03</v>
       </c>
       <c r="M78">
-        <v>2.7239616</v>
+        <v>2.7598032</v>
       </c>
       <c r="N78">
-        <v>-1.6939616</v>
+        <v>-1.7298032</v>
       </c>
       <c r="O78">
-        <v>-0.457369632</v>
+        <v>-0.467046864</v>
       </c>
       <c r="P78">
-        <v>-1.236591968</v>
+        <v>-1.262756336</v>
       </c>
       <c r="Q78">
-        <v>-1.206591968</v>
+        <v>-1.232756336</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4558941538746613</v>
+        <v>0.4737243344779074</v>
       </c>
       <c r="T78">
-        <v>4.912822292216508</v>
+        <v>5.126423261443312</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1020939502230868</v>
+        <v>0.1007680547656442</v>
       </c>
       <c r="W78">
-        <v>0.2117262465373961</v>
+        <v>0.2120388926862611</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3781257415669883</v>
+        <v>0.373215017650534</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2722265442983398</v>
+        <v>0.2741265442983398</v>
       </c>
       <c r="C79">
-        <v>-3.710969342612535</v>
+        <v>-3.916418048222036</v>
       </c>
       <c r="D79">
-        <v>6.423030657387463</v>
+        <v>6.369581951777963</v>
       </c>
       <c r="E79">
-        <v>11.704</v>
+        <v>11.856</v>
       </c>
       <c r="F79">
-        <v>11.704</v>
+        <v>11.856</v>
       </c>
       <c r="G79">
         <v>1.57</v>
@@ -7765,37 +7765,37 @@
         <v>1.03</v>
       </c>
       <c r="M79">
-        <v>2.7598032</v>
+        <v>2.7956448</v>
       </c>
       <c r="N79">
-        <v>-1.7298032</v>
+        <v>-1.7656448</v>
       </c>
       <c r="O79">
-        <v>-0.467046864</v>
+        <v>-0.4767240960000001</v>
       </c>
       <c r="P79">
-        <v>-1.262756336</v>
+        <v>-1.288920704</v>
       </c>
       <c r="Q79">
-        <v>-1.232756336</v>
+        <v>-1.258920704</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4737243344779074</v>
+        <v>0.4931754405905396</v>
       </c>
       <c r="T79">
-        <v>5.126423261443312</v>
+        <v>5.359442500599827</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1007680547656442</v>
+        <v>0.09947615662762307</v>
       </c>
       <c r="W79">
-        <v>0.2120388926862611</v>
+        <v>0.2123435222672065</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.373215017650534</v>
+        <v>0.3684302097319373</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2741265442983398</v>
+        <v>0.2760265442983397</v>
       </c>
       <c r="C80">
-        <v>-3.916418048222036</v>
+        <v>-4.120984557202403</v>
       </c>
       <c r="D80">
-        <v>6.369581951777963</v>
+        <v>6.317015442797596</v>
       </c>
       <c r="E80">
-        <v>11.856</v>
+        <v>12.008</v>
       </c>
       <c r="F80">
-        <v>11.856</v>
+        <v>12.008</v>
       </c>
       <c r="G80">
         <v>1.57</v>
@@ -7847,37 +7847,37 @@
         <v>1.03</v>
       </c>
       <c r="M80">
-        <v>2.7956448</v>
+        <v>2.8314864</v>
       </c>
       <c r="N80">
-        <v>-1.7656448</v>
+        <v>-1.8014864</v>
       </c>
       <c r="O80">
-        <v>-0.4767240960000001</v>
+        <v>-0.486401328</v>
       </c>
       <c r="P80">
-        <v>-1.288920704</v>
+        <v>-1.315085072</v>
       </c>
       <c r="Q80">
-        <v>-1.258920704</v>
+        <v>-1.285085072</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4931754405905396</v>
+        <v>0.514479032999613</v>
       </c>
       <c r="T80">
-        <v>5.359442500599827</v>
+        <v>5.614654048247439</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09947615662762307</v>
+        <v>0.09821696477157724</v>
       </c>
       <c r="W80">
-        <v>0.2123435222672065</v>
+        <v>0.2126404397068621</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3684302097319373</v>
+        <v>0.3637665361910267</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2760265442983397</v>
+        <v>0.2779265442983397</v>
       </c>
       <c r="C81">
-        <v>-4.120984557202403</v>
+        <v>-4.324690532396217</v>
       </c>
       <c r="D81">
-        <v>6.317015442797596</v>
+        <v>6.265309467603783</v>
       </c>
       <c r="E81">
-        <v>12.008</v>
+        <v>12.16</v>
       </c>
       <c r="F81">
-        <v>12.008</v>
+        <v>12.16</v>
       </c>
       <c r="G81">
         <v>1.57</v>
@@ -7929,37 +7929,37 @@
         <v>1.03</v>
       </c>
       <c r="M81">
-        <v>2.8314864</v>
+        <v>2.867328</v>
       </c>
       <c r="N81">
-        <v>-1.8014864</v>
+        <v>-1.837328</v>
       </c>
       <c r="O81">
-        <v>-0.486401328</v>
+        <v>-0.4960785600000001</v>
       </c>
       <c r="P81">
-        <v>-1.315085072</v>
+        <v>-1.34124944</v>
       </c>
       <c r="Q81">
-        <v>-1.285085072</v>
+        <v>-1.31124944</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.514479032999613</v>
+        <v>0.5379129846495936</v>
       </c>
       <c r="T81">
-        <v>5.614654048247439</v>
+        <v>5.89538675065981</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09821696477157724</v>
+        <v>0.09698925271193251</v>
       </c>
       <c r="W81">
-        <v>0.2126404397068621</v>
+        <v>0.2129299342105263</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3637665361910267</v>
+        <v>0.3592194544886389</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2779265442983397</v>
+        <v>0.2798265442983398</v>
       </c>
       <c r="C82">
-        <v>-4.324690532396217</v>
+        <v>-4.527556933146347</v>
       </c>
       <c r="D82">
-        <v>6.265309467603783</v>
+        <v>6.214443066853653</v>
       </c>
       <c r="E82">
-        <v>12.16</v>
+        <v>12.312</v>
       </c>
       <c r="F82">
-        <v>12.16</v>
+        <v>12.312</v>
       </c>
       <c r="G82">
         <v>1.57</v>
@@ -8011,37 +8011,37 @@
         <v>1.03</v>
       </c>
       <c r="M82">
-        <v>2.867328</v>
+        <v>2.9031696</v>
       </c>
       <c r="N82">
-        <v>-1.837328</v>
+        <v>-1.8731696</v>
       </c>
       <c r="O82">
-        <v>-0.4960785600000001</v>
+        <v>-0.505755792</v>
       </c>
       <c r="P82">
-        <v>-1.34124944</v>
+        <v>-1.367413808</v>
       </c>
       <c r="Q82">
-        <v>-1.31124944</v>
+        <v>-1.337413808</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5379129846495936</v>
+        <v>0.5638136680522038</v>
       </c>
       <c r="T82">
-        <v>5.89538675065981</v>
+        <v>6.205670263852432</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09698925271193251</v>
+        <v>0.09579185453030371</v>
       </c>
       <c r="W82">
-        <v>0.2129299342105263</v>
+        <v>0.2132122807017544</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3592194544886389</v>
+        <v>0.3547846464085322</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2798265442983398</v>
+        <v>0.2817265442983398</v>
       </c>
       <c r="C83">
-        <v>-4.527556933146347</v>
+        <v>-4.729604043623628</v>
       </c>
       <c r="D83">
-        <v>6.214443066853653</v>
+        <v>6.164395956376373</v>
       </c>
       <c r="E83">
-        <v>12.312</v>
+        <v>12.464</v>
       </c>
       <c r="F83">
-        <v>12.312</v>
+        <v>12.464</v>
       </c>
       <c r="G83">
         <v>1.57</v>
@@ -8093,37 +8093,37 @@
         <v>1.03</v>
       </c>
       <c r="M83">
-        <v>2.9031696</v>
+        <v>2.9390112</v>
       </c>
       <c r="N83">
-        <v>-1.8731696</v>
+        <v>-1.9090112</v>
       </c>
       <c r="O83">
-        <v>-0.505755792</v>
+        <v>-0.5154330240000001</v>
       </c>
       <c r="P83">
-        <v>-1.367413808</v>
+        <v>-1.393578176</v>
       </c>
       <c r="Q83">
-        <v>-1.337413808</v>
+        <v>-1.363578176</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5638136680522038</v>
+        <v>0.5925922051662151</v>
       </c>
       <c r="T83">
-        <v>6.205670263852432</v>
+        <v>6.550429722955346</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09579185453030371</v>
+        <v>0.09462366118237317</v>
       </c>
       <c r="W83">
-        <v>0.2132122807017544</v>
+        <v>0.2134877406931964</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3547846464085322</v>
+        <v>0.3504580043791599</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2817265442983398</v>
+        <v>0.2836265442983398</v>
       </c>
       <c r="C84">
-        <v>-4.729604043623628</v>
+        <v>-4.930851499796655</v>
       </c>
       <c r="D84">
-        <v>6.164395956376373</v>
+        <v>6.115148500203344</v>
       </c>
       <c r="E84">
-        <v>12.464</v>
+        <v>12.616</v>
       </c>
       <c r="F84">
-        <v>12.464</v>
+        <v>12.616</v>
       </c>
       <c r="G84">
         <v>1.57</v>
@@ -8175,37 +8175,37 @@
         <v>1.03</v>
       </c>
       <c r="M84">
-        <v>2.9390112</v>
+        <v>2.9748528</v>
       </c>
       <c r="N84">
-        <v>-1.9090112</v>
+        <v>-1.9448528</v>
       </c>
       <c r="O84">
-        <v>-0.5154330240000001</v>
+        <v>-0.5251102559999999</v>
       </c>
       <c r="P84">
-        <v>-1.393578176</v>
+        <v>-1.419742544</v>
       </c>
       <c r="Q84">
-        <v>-1.363578176</v>
+        <v>-1.389742544</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5925922051662151</v>
+        <v>0.6247564525289336</v>
       </c>
       <c r="T84">
-        <v>6.550429722955346</v>
+        <v>6.935749118423307</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09462366118237317</v>
+        <v>0.09348361707174219</v>
       </c>
       <c r="W84">
-        <v>0.2134877406931964</v>
+        <v>0.2137565630944832</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3504580043791599</v>
+        <v>0.3462356187842303</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2836265442983398</v>
+        <v>0.2855265442983398</v>
       </c>
       <c r="C85">
-        <v>-4.930851499796655</v>
+        <v>-5.131318315119064</v>
       </c>
       <c r="D85">
-        <v>6.115148500203344</v>
+        <v>6.066681684880937</v>
       </c>
       <c r="E85">
-        <v>12.616</v>
+        <v>12.768</v>
       </c>
       <c r="F85">
-        <v>12.616</v>
+        <v>12.768</v>
       </c>
       <c r="G85">
         <v>1.57</v>
@@ -8257,37 +8257,37 @@
         <v>1.03</v>
       </c>
       <c r="M85">
-        <v>2.9748528</v>
+        <v>3.0106944</v>
       </c>
       <c r="N85">
-        <v>-1.9448528</v>
+        <v>-1.9806944</v>
       </c>
       <c r="O85">
-        <v>-0.5251102559999999</v>
+        <v>-0.5347874880000001</v>
       </c>
       <c r="P85">
-        <v>-1.419742544</v>
+        <v>-1.445906912</v>
       </c>
       <c r="Q85">
-        <v>-1.389742544</v>
+        <v>-1.415906912</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6247564525289336</v>
+        <v>0.6609412308119922</v>
       </c>
       <c r="T85">
-        <v>6.935749118423307</v>
+        <v>7.369233438324765</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09348361707174219</v>
+        <v>0.09237071686850715</v>
       </c>
       <c r="W85">
-        <v>0.2137565630944832</v>
+        <v>0.214018984962406</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3462356187842303</v>
+        <v>0.3421137661796561</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2855265442983397</v>
+        <v>0.2874265442983397</v>
       </c>
       <c r="C86">
-        <v>-5.13131831511906</v>
+        <v>-5.331022905004855</v>
       </c>
       <c r="D86">
-        <v>6.066681684880939</v>
+        <v>6.018977094995145</v>
       </c>
       <c r="E86">
-        <v>12.768</v>
+        <v>12.92</v>
       </c>
       <c r="F86">
-        <v>12.768</v>
+        <v>12.92</v>
       </c>
       <c r="G86">
         <v>1.57</v>
@@ -8339,37 +8339,37 @@
         <v>1.03</v>
       </c>
       <c r="M86">
-        <v>3.0106944</v>
+        <v>3.046536</v>
       </c>
       <c r="N86">
-        <v>-1.9806944</v>
+        <v>-2.016536</v>
       </c>
       <c r="O86">
-        <v>-0.534787488</v>
+        <v>-0.5444647200000001</v>
       </c>
       <c r="P86">
-        <v>-1.445906912</v>
+        <v>-1.47207128</v>
       </c>
       <c r="Q86">
-        <v>-1.415906912</v>
+        <v>-1.44207128</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6609412308119917</v>
+        <v>0.7019506461994579</v>
       </c>
       <c r="T86">
-        <v>7.36923343832476</v>
+        <v>7.860515667546411</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09237071686850716</v>
+        <v>0.09128400255240707</v>
       </c>
       <c r="W86">
-        <v>0.214018984962406</v>
+        <v>0.2142752321981424</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3421137661796562</v>
+        <v>0.3380888983422483</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2874265442983397</v>
+        <v>0.2893265442983397</v>
       </c>
       <c r="C87">
-        <v>-5.331022905004855</v>
+        <v>-5.529983110158016</v>
       </c>
       <c r="D87">
-        <v>6.018977094995145</v>
+        <v>5.972016889841983</v>
       </c>
       <c r="E87">
-        <v>12.92</v>
+        <v>13.072</v>
       </c>
       <c r="F87">
-        <v>12.92</v>
+        <v>13.072</v>
       </c>
       <c r="G87">
         <v>1.57</v>
@@ -8421,37 +8421,37 @@
         <v>1.03</v>
       </c>
       <c r="M87">
-        <v>3.046536</v>
+        <v>3.0823776</v>
       </c>
       <c r="N87">
-        <v>-2.016536</v>
+        <v>-2.0523776</v>
       </c>
       <c r="O87">
-        <v>-0.5444647200000001</v>
+        <v>-0.5541419519999999</v>
       </c>
       <c r="P87">
-        <v>-1.47207128</v>
+        <v>-1.498235648</v>
       </c>
       <c r="Q87">
-        <v>-1.44207128</v>
+        <v>-1.468235648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7019506461994579</v>
+        <v>0.7488185494994192</v>
       </c>
       <c r="T87">
-        <v>7.860515667546411</v>
+        <v>8.421981072371155</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09128400255240707</v>
+        <v>0.09022256066226281</v>
       </c>
       <c r="W87">
-        <v>0.2142752321981424</v>
+        <v>0.2145255201958384</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3380888983422483</v>
+        <v>0.3341576320824549</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2893265442983397</v>
+        <v>0.2912265442983398</v>
       </c>
       <c r="C88">
-        <v>-5.529983110158016</v>
+        <v>-5.728216218818451</v>
       </c>
       <c r="D88">
-        <v>5.972016889841983</v>
+        <v>5.925783781181549</v>
       </c>
       <c r="E88">
-        <v>13.072</v>
+        <v>13.224</v>
       </c>
       <c r="F88">
-        <v>13.072</v>
+        <v>13.224</v>
       </c>
       <c r="G88">
         <v>1.57</v>
@@ -8503,37 +8503,37 @@
         <v>1.03</v>
       </c>
       <c r="M88">
-        <v>3.0823776</v>
+        <v>3.1182192</v>
       </c>
       <c r="N88">
-        <v>-2.0523776</v>
+        <v>-2.0882192</v>
       </c>
       <c r="O88">
-        <v>-0.5541419519999999</v>
+        <v>-0.5638191840000001</v>
       </c>
       <c r="P88">
-        <v>-1.498235648</v>
+        <v>-1.524400016</v>
       </c>
       <c r="Q88">
-        <v>-1.468235648</v>
+        <v>-1.494400016</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7488185494994192</v>
+        <v>0.802896899460913</v>
       </c>
       <c r="T88">
-        <v>8.421981072371155</v>
+        <v>9.06982577024586</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09022256066226281</v>
+        <v>0.08918551973511035</v>
       </c>
       <c r="W88">
-        <v>0.2145255201958384</v>
+        <v>0.214770054446461</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3341576320824549</v>
+        <v>0.3303167397596679</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2912265442983398</v>
+        <v>0.2931265442983397</v>
       </c>
       <c r="C89">
-        <v>-5.728216218818451</v>
+        <v>-5.925738987982538</v>
       </c>
       <c r="D89">
-        <v>5.925783781181549</v>
+        <v>5.880261012017461</v>
       </c>
       <c r="E89">
-        <v>13.224</v>
+        <v>13.376</v>
       </c>
       <c r="F89">
-        <v>13.224</v>
+        <v>13.376</v>
       </c>
       <c r="G89">
         <v>1.57</v>
@@ -8585,37 +8585,37 @@
         <v>1.03</v>
       </c>
       <c r="M89">
-        <v>3.1182192</v>
+        <v>3.1540608</v>
       </c>
       <c r="N89">
-        <v>-2.0882192</v>
+        <v>-2.1240608</v>
       </c>
       <c r="O89">
-        <v>-0.5638191840000001</v>
+        <v>-0.5734964159999999</v>
       </c>
       <c r="P89">
-        <v>-1.524400016</v>
+        <v>-1.550564384</v>
       </c>
       <c r="Q89">
-        <v>-1.494400016</v>
+        <v>-1.520564384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.802896899460913</v>
+        <v>0.8659883077493226</v>
       </c>
       <c r="T89">
-        <v>9.06982577024586</v>
+        <v>9.825644584433016</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08918551973511035</v>
+        <v>0.08817204791993864</v>
       </c>
       <c r="W89">
-        <v>0.214770054446461</v>
+        <v>0.2150090311004785</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3303167397596679</v>
+        <v>0.3265631404442173</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2931265442983397</v>
+        <v>0.2950265442983397</v>
       </c>
       <c r="C90">
-        <v>-5.925738987982538</v>
+        <v>-6.122567663653051</v>
       </c>
       <c r="D90">
-        <v>5.880261012017461</v>
+        <v>5.835432336346948</v>
       </c>
       <c r="E90">
-        <v>13.376</v>
+        <v>13.528</v>
       </c>
       <c r="F90">
-        <v>13.376</v>
+        <v>13.528</v>
       </c>
       <c r="G90">
         <v>1.57</v>
@@ -8667,37 +8667,37 @@
         <v>1.03</v>
       </c>
       <c r="M90">
-        <v>3.1540608</v>
+        <v>3.1899024</v>
       </c>
       <c r="N90">
-        <v>-2.1240608</v>
+        <v>-2.1599024</v>
       </c>
       <c r="O90">
-        <v>-0.5734964159999999</v>
+        <v>-0.583173648</v>
       </c>
       <c r="P90">
-        <v>-1.550564384</v>
+        <v>-1.576728752</v>
       </c>
       <c r="Q90">
-        <v>-1.520564384</v>
+        <v>-1.546728752</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8659883077493226</v>
+        <v>0.9405508811810791</v>
       </c>
       <c r="T90">
-        <v>9.825644584433016</v>
+        <v>10.71888500119965</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08817204791993864</v>
+        <v>0.08718135075229889</v>
       </c>
       <c r="W90">
-        <v>0.2150090311004785</v>
+        <v>0.2152426374926079</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3265631404442173</v>
+        <v>0.322893891675181</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2950265442983397</v>
+        <v>0.2969265442983398</v>
       </c>
       <c r="C91">
-        <v>-6.122567663653051</v>
+        <v>-6.318718000169799</v>
       </c>
       <c r="D91">
-        <v>5.835432336346948</v>
+        <v>5.791281999830201</v>
       </c>
       <c r="E91">
-        <v>13.528</v>
+        <v>13.68</v>
       </c>
       <c r="F91">
-        <v>13.528</v>
+        <v>13.68</v>
       </c>
       <c r="G91">
         <v>1.57</v>
@@ -8749,37 +8749,37 @@
         <v>1.03</v>
       </c>
       <c r="M91">
-        <v>3.1899024</v>
+        <v>3.225744</v>
       </c>
       <c r="N91">
-        <v>-2.1599024</v>
+        <v>-2.195744</v>
       </c>
       <c r="O91">
-        <v>-0.583173648</v>
+        <v>-0.5928508800000002</v>
       </c>
       <c r="P91">
-        <v>-1.576728752</v>
+        <v>-1.60289312</v>
       </c>
       <c r="Q91">
-        <v>-1.546728752</v>
+        <v>-1.57289312</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9405508811810791</v>
+        <v>1.030025969299187</v>
       </c>
       <c r="T91">
-        <v>10.71888500119965</v>
+        <v>11.79077350131962</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08718135075229889</v>
+        <v>0.08621266907727333</v>
       </c>
       <c r="W91">
-        <v>0.2152426374926079</v>
+        <v>0.215471052631579</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.322893891675181</v>
+        <v>0.319306181767679</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2969265442983398</v>
+        <v>0.2988265442983398</v>
       </c>
       <c r="C92">
-        <v>-6.318718000169799</v>
+        <v>-6.514205278669335</v>
       </c>
       <c r="D92">
-        <v>5.791281999830201</v>
+        <v>5.747794721330663</v>
       </c>
       <c r="E92">
-        <v>13.68</v>
+        <v>13.832</v>
       </c>
       <c r="F92">
-        <v>13.68</v>
+        <v>13.832</v>
       </c>
       <c r="G92">
         <v>1.57</v>
@@ -8831,37 +8831,37 @@
         <v>1.03</v>
       </c>
       <c r="M92">
-        <v>3.225744</v>
+        <v>3.2615856</v>
       </c>
       <c r="N92">
-        <v>-2.195744</v>
+        <v>-2.2315856</v>
       </c>
       <c r="O92">
-        <v>-0.5928508800000002</v>
+        <v>-0.602528112</v>
       </c>
       <c r="P92">
-        <v>-1.60289312</v>
+        <v>-1.629057488</v>
       </c>
       <c r="Q92">
-        <v>-1.57289312</v>
+        <v>-1.599057488</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.030025969299187</v>
+        <v>1.13938441033243</v>
       </c>
       <c r="T92">
-        <v>11.79077350131962</v>
+        <v>13.10085944591069</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08621266907727333</v>
+        <v>0.08526527710939122</v>
       </c>
       <c r="W92">
-        <v>0.215471052631579</v>
+        <v>0.2156944476576056</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.319306181767679</v>
+        <v>0.3157973226273749</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2988265442983398</v>
+        <v>0.3007265442983398</v>
       </c>
       <c r="C93">
-        <v>-6.514205278669335</v>
+        <v>-6.709044324719197</v>
       </c>
       <c r="D93">
-        <v>5.747794721330663</v>
+        <v>5.704955675280803</v>
       </c>
       <c r="E93">
-        <v>13.832</v>
+        <v>13.984</v>
       </c>
       <c r="F93">
-        <v>13.832</v>
+        <v>13.984</v>
       </c>
       <c r="G93">
         <v>1.57</v>
@@ -8913,37 +8913,37 @@
         <v>1.03</v>
       </c>
       <c r="M93">
-        <v>3.2615856</v>
+        <v>3.2974272</v>
       </c>
       <c r="N93">
-        <v>-2.2315856</v>
+        <v>-2.2674272</v>
       </c>
       <c r="O93">
-        <v>-0.602528112</v>
+        <v>-0.612205344</v>
       </c>
       <c r="P93">
-        <v>-1.629057488</v>
+        <v>-1.655221856</v>
       </c>
       <c r="Q93">
-        <v>-1.599057488</v>
+        <v>-1.625221856</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.13938441033243</v>
+        <v>1.276082461623985</v>
       </c>
       <c r="T93">
-        <v>13.10085944591069</v>
+        <v>14.73846687664953</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08526527710939122</v>
+        <v>0.08433848061907176</v>
       </c>
       <c r="W93">
-        <v>0.2156944476576056</v>
+        <v>0.2159129862700229</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3157973226273749</v>
+        <v>0.312364743033599</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3007265442983398</v>
+        <v>0.3026265442983398</v>
       </c>
       <c r="C94">
-        <v>-6.709044324719197</v>
+        <v>-6.903249525169357</v>
       </c>
       <c r="D94">
-        <v>5.704955675280803</v>
+        <v>5.662750474830642</v>
       </c>
       <c r="E94">
-        <v>13.984</v>
+        <v>14.136</v>
       </c>
       <c r="F94">
-        <v>13.984</v>
+        <v>14.136</v>
       </c>
       <c r="G94">
         <v>1.57</v>
@@ -8995,37 +8995,37 @@
         <v>1.03</v>
       </c>
       <c r="M94">
-        <v>3.2974272</v>
+        <v>3.3332688</v>
       </c>
       <c r="N94">
-        <v>-2.2674272</v>
+        <v>-2.3032688</v>
       </c>
       <c r="O94">
-        <v>-0.612205344</v>
+        <v>-0.621882576</v>
       </c>
       <c r="P94">
-        <v>-1.655221856</v>
+        <v>-1.681386224</v>
       </c>
       <c r="Q94">
-        <v>-1.625221856</v>
+        <v>-1.651386224</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.276082461623985</v>
+        <v>1.45183709899884</v>
       </c>
       <c r="T94">
-        <v>14.73846687664953</v>
+        <v>16.84396214474232</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08433848061907176</v>
+        <v>0.08343161523607098</v>
       </c>
       <c r="W94">
-        <v>0.2159129862700229</v>
+        <v>0.2161268251273345</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.312364743033599</v>
+        <v>0.3090059823558184</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3026265442983398</v>
+        <v>0.3045265442983398</v>
       </c>
       <c r="C95">
-        <v>-6.903249525169357</v>
+        <v>-7.096834844261207</v>
       </c>
       <c r="D95">
-        <v>5.662750474830642</v>
+        <v>5.621165155738793</v>
       </c>
       <c r="E95">
-        <v>14.136</v>
+        <v>14.288</v>
       </c>
       <c r="F95">
-        <v>14.136</v>
+        <v>14.288</v>
       </c>
       <c r="G95">
         <v>1.57</v>
@@ -9077,37 +9077,37 @@
         <v>1.03</v>
       </c>
       <c r="M95">
-        <v>3.3332688</v>
+        <v>3.3691104</v>
       </c>
       <c r="N95">
-        <v>-2.3032688</v>
+        <v>-2.3391104</v>
       </c>
       <c r="O95">
-        <v>-0.621882576</v>
+        <v>-0.631559808</v>
       </c>
       <c r="P95">
-        <v>-1.681386224</v>
+        <v>-1.707550592</v>
       </c>
       <c r="Q95">
-        <v>-1.651386224</v>
+        <v>-1.677550592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.45183709899884</v>
+        <v>1.686176615498646</v>
       </c>
       <c r="T95">
-        <v>16.84396214474232</v>
+        <v>19.65128916886605</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08343161523607098</v>
+        <v>0.08254404486121915</v>
       </c>
       <c r="W95">
-        <v>0.2161268251273345</v>
+        <v>0.2163361142217245</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3090059823558184</v>
+        <v>0.3057186846711821</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3045265442983398</v>
+        <v>0.3064265442983398</v>
       </c>
       <c r="C96">
-        <v>-7.096834844261207</v>
+        <v>-7.289813839031894</v>
       </c>
       <c r="D96">
-        <v>5.621165155738793</v>
+        <v>5.580186160968105</v>
       </c>
       <c r="E96">
-        <v>14.288</v>
+        <v>14.44</v>
       </c>
       <c r="F96">
-        <v>14.288</v>
+        <v>14.44</v>
       </c>
       <c r="G96">
         <v>1.57</v>
@@ -9159,37 +9159,37 @@
         <v>1.03</v>
       </c>
       <c r="M96">
-        <v>3.3691104</v>
+        <v>3.404952</v>
       </c>
       <c r="N96">
-        <v>-2.3391104</v>
+        <v>-2.374952</v>
       </c>
       <c r="O96">
-        <v>-0.631559808</v>
+        <v>-0.6412370400000001</v>
       </c>
       <c r="P96">
-        <v>-1.707550592</v>
+        <v>-1.73371496</v>
       </c>
       <c r="Q96">
-        <v>-1.677550592</v>
+        <v>-1.70371496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.686176615498646</v>
+        <v>2.014251938598377</v>
       </c>
       <c r="T96">
-        <v>19.65128916886605</v>
+        <v>23.58154700263927</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08254404486121915</v>
+        <v>0.08167516017846947</v>
       </c>
       <c r="W96">
-        <v>0.2163361142217245</v>
+        <v>0.2165409972299169</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3057186846711821</v>
+        <v>0.3025005932535906</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3064265442983398</v>
+        <v>0.3083265442983398</v>
       </c>
       <c r="C97">
-        <v>-7.289813839031894</v>
+        <v>-7.482199674049746</v>
       </c>
       <c r="D97">
-        <v>5.580186160968105</v>
+        <v>5.539800325950254</v>
       </c>
       <c r="E97">
-        <v>14.44</v>
+        <v>14.592</v>
       </c>
       <c r="F97">
-        <v>14.44</v>
+        <v>14.592</v>
       </c>
       <c r="G97">
         <v>1.57</v>
@@ -9241,37 +9241,37 @@
         <v>1.03</v>
       </c>
       <c r="M97">
-        <v>3.404952</v>
+        <v>3.4407936</v>
       </c>
       <c r="N97">
-        <v>-2.374952</v>
+        <v>-2.4107936</v>
       </c>
       <c r="O97">
-        <v>-0.6412370400000001</v>
+        <v>-0.650914272</v>
       </c>
       <c r="P97">
-        <v>-1.73371496</v>
+        <v>-1.759879328</v>
       </c>
       <c r="Q97">
-        <v>-1.70371496</v>
+        <v>-1.729879328</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.014251938598377</v>
+        <v>2.506364923247972</v>
       </c>
       <c r="T97">
-        <v>23.58154700263927</v>
+        <v>29.4769337532991</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08167516017846947</v>
+        <v>0.08082437725994376</v>
       </c>
       <c r="W97">
-        <v>0.2165409972299169</v>
+        <v>0.2167416118421053</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3025005932535906</v>
+        <v>0.2993495454071992</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3083265442983397</v>
+        <v>0.3102265442983397</v>
       </c>
       <c r="C98">
-        <v>-7.482199674049743</v>
+        <v>-7.674005135514422</v>
       </c>
       <c r="D98">
-        <v>5.539800325950256</v>
+        <v>5.499994864485577</v>
       </c>
       <c r="E98">
-        <v>14.592</v>
+        <v>14.744</v>
       </c>
       <c r="F98">
-        <v>14.592</v>
+        <v>14.744</v>
       </c>
       <c r="G98">
         <v>1.57</v>
@@ -9323,37 +9323,37 @@
         <v>1.03</v>
       </c>
       <c r="M98">
-        <v>3.4407936</v>
+        <v>3.4766352</v>
       </c>
       <c r="N98">
-        <v>-2.4107936</v>
+        <v>-2.4466352</v>
       </c>
       <c r="O98">
-        <v>-0.650914272</v>
+        <v>-0.6605915040000001</v>
       </c>
       <c r="P98">
-        <v>-1.759879328</v>
+        <v>-1.786043696</v>
       </c>
       <c r="Q98">
-        <v>-1.729879328</v>
+        <v>-1.756043696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.506364923247965</v>
+        <v>3.326553230997287</v>
       </c>
       <c r="T98">
-        <v>29.47693375329902</v>
+        <v>39.30257833773203</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08082437725994376</v>
+        <v>0.07999113625726392</v>
       </c>
       <c r="W98">
-        <v>0.2167416118421053</v>
+        <v>0.2169380900705372</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.299349545407199</v>
+        <v>0.296263467619496</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3102265442983397</v>
+        <v>0.3121265442983397</v>
       </c>
       <c r="C99">
-        <v>-7.674005135514422</v>
+        <v>-7.865242644753518</v>
       </c>
       <c r="D99">
-        <v>5.499994864485577</v>
+        <v>5.460757355246481</v>
       </c>
       <c r="E99">
-        <v>14.744</v>
+        <v>14.896</v>
       </c>
       <c r="F99">
-        <v>14.744</v>
+        <v>14.896</v>
       </c>
       <c r="G99">
         <v>1.57</v>
@@ -9405,37 +9405,37 @@
         <v>1.03</v>
       </c>
       <c r="M99">
-        <v>3.4766352</v>
+        <v>3.5124768</v>
       </c>
       <c r="N99">
-        <v>-2.4466352</v>
+        <v>-2.4824768</v>
       </c>
       <c r="O99">
-        <v>-0.6605915040000001</v>
+        <v>-0.6702687359999999</v>
       </c>
       <c r="P99">
-        <v>-1.786043696</v>
+        <v>-1.812208064</v>
       </c>
       <c r="Q99">
-        <v>-1.756043696</v>
+        <v>-1.782208064</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.326553230997287</v>
+        <v>4.966929846495931</v>
       </c>
       <c r="T99">
-        <v>39.30257833773203</v>
+        <v>58.95386750659804</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07999113625726392</v>
+        <v>0.07917490017300613</v>
       </c>
       <c r="W99">
-        <v>0.2169380900705372</v>
+        <v>0.2171305585392052</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.296263467619496</v>
+        <v>0.2932403710111339</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3121265442983397</v>
+        <v>0.3140265442983398</v>
       </c>
       <c r="C100">
-        <v>-7.865242644753518</v>
+        <v>-8.055924271145528</v>
       </c>
       <c r="D100">
-        <v>5.460757355246481</v>
+        <v>5.422075728854471</v>
       </c>
       <c r="E100">
-        <v>14.896</v>
+        <v>15.048</v>
       </c>
       <c r="F100">
-        <v>14.896</v>
+        <v>15.048</v>
       </c>
       <c r="G100">
         <v>1.57</v>
@@ -9487,37 +9487,37 @@
         <v>1.03</v>
       </c>
       <c r="M100">
-        <v>3.5124768</v>
+        <v>3.5483184</v>
       </c>
       <c r="N100">
-        <v>-2.4824768</v>
+        <v>-2.5183184</v>
       </c>
       <c r="O100">
-        <v>-0.6702687359999999</v>
+        <v>-0.6799459680000001</v>
       </c>
       <c r="P100">
-        <v>-1.812208064</v>
+        <v>-1.838372432</v>
       </c>
       <c r="Q100">
-        <v>-1.782208064</v>
+        <v>-1.808372432</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.966929846495931</v>
+        <v>9.888059692991861</v>
       </c>
       <c r="T100">
-        <v>58.95386750659804</v>
+        <v>117.9077350131961</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07917490017300613</v>
+        <v>0.07837515370661213</v>
       </c>
       <c r="W100">
-        <v>0.2171305585392052</v>
+        <v>0.2173191387559809</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2932403710111339</v>
+        <v>0.2902783470615264</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3140265442983398</v>
-      </c>
-      <c r="C101">
-        <v>-8.055924271145528</v>
-      </c>
-      <c r="D101">
-        <v>5.422075728854471</v>
-      </c>
-      <c r="E101">
-        <v>15.048</v>
-      </c>
-      <c r="F101">
-        <v>15.048</v>
-      </c>
-      <c r="G101">
-        <v>1.57</v>
-      </c>
-      <c r="H101">
-        <v>15.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.06</v>
-      </c>
-      <c r="K101">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="L101">
-        <v>1.03</v>
-      </c>
-      <c r="M101">
-        <v>3.5483184</v>
-      </c>
-      <c r="N101">
-        <v>-2.5183184</v>
-      </c>
-      <c r="O101">
-        <v>-0.6799459680000001</v>
-      </c>
-      <c r="P101">
-        <v>-1.838372432</v>
-      </c>
-      <c r="Q101">
-        <v>-1.808372432</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.888059692991861</v>
-      </c>
-      <c r="T101">
-        <v>117.9077350131961</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07837515370661213</v>
-      </c>
-      <c r="W101">
-        <v>0.2173191387559809</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2902783470615264</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
